--- a/cia-facbook-pwa/FACTBOOK_FMCG_2026_TOTALEMENT_A_JOUR.xlsx
+++ b/cia-facbook-pwa/FACTBOOK_FMCG_2026_TOTALEMENT_A_JOUR.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Factbook FMCG 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Factbook FMCG 2026'!$A$1:$AG$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Factbook FMCG 2026'!$A$1:$AI$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -72,12 +72,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -445,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG45"/>
+  <dimension ref="A1:AI45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -481,6 +487,8 @@
     <col width="25" customWidth="1" min="31" max="31"/>
     <col width="25" customWidth="1" min="32" max="32"/>
     <col width="25" customWidth="1" min="33" max="33"/>
+    <col width="25" customWidth="1" min="34" max="34"/>
+    <col width="25" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,160 +499,170 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Main_Cluster</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sub_Cluster</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Area (land): sq km</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Population (2025 est.)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Population growth rate (2025 est.)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Age structure 0-14 years</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Age structure 15-64 years</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Age structure &gt;= 65 years</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Median age</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>urban population</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Ethnic Groups</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Religions</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Languages</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Literacy (Total)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Literacy (Male)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Literacy (Female)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Administrative division</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>GDP (2024 est.) official ex rate</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>GDP growth rate (2024est.)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>GDP per capita (2019 est.)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Unemployment rate</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Population below poverty line</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Household income or consumption by percentage share</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Inflation rate (2024 est.)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Mobile cellular users (2019 est)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Mobile cellular (pourcentage population)</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Internet users (2018 est)</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Internet users (pourcentage population)</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Radio brodacast stations</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>TV broadcast stations</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Source: CIA The World Factbook (Last update: 2021) June 2021</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>below 14years</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Below Poverty line</t>
         </is>
@@ -656,123 +674,133 @@
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>910768</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>244344065</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="F2" s="4" t="n">
         <v>0.0239</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>0.404</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="H2" s="4" t="n">
         <v>0.5620000000000001</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="I2" s="4" t="n">
         <v>0.034</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>19.4 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="K2" s="4" t="n">
         <v>0.5429999999999999</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Hausa 30%, Yoruba 15.5%, Igbo (Ibo) 15.2%, Fulani 6%, Tiv 2.4%, Kanuri/Beriberi 2.4%, Ibibio 1.8%, Ijaw/Izon 1.8%, other 24.9% (2018 est.)</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Muslim 53.5%, Roman Catholic 10.6%, other Christian 35.3%, other 0.6% (2018 est.)</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>English (official), Hausa, Yoruba, Igbo (Ibo), Fulani, over 500 additional indigenous languages</t>
         </is>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="O2" s="4" t="n">
         <v>0.632</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="P2" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">41,5% </t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>36 states</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>$187.76 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="T2" s="4" t="n">
         <v>0.034</v>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>$5,700 (2024 est.)</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>3% (2024 est.)</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>40,1% (2018 est.)</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2,9%
 highest 10%: 26.7% (2018 est.)</t>
         </is>
       </c>
-      <c r="W2" s="2" t="n">
+      <c r="Y2" s="4" t="n">
         <v>0.332</v>
       </c>
-      <c r="X2" s="2" t="n">
+      <c r="Z2" s="3" t="n">
         <v>165000000</v>
       </c>
-      <c r="Y2" s="2" t="n">
+      <c r="AA2" s="4" t="n">
         <v>0.6752772980182679</v>
       </c>
-      <c r="Z2" s="2" t="n">
+      <c r="AB2" s="3" t="n">
         <v>95294185.35000001</v>
       </c>
-      <c r="AA2" s="2" t="n">
+      <c r="AC2" s="4" t="n">
         <v>0.39</v>
       </c>
-      <c r="AB2" s="2" t="n">
+      <c r="AD2" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="AC2" s="2" t="n">
+      <c r="AE2" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="AD2" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE2" s="2" t="n">
+      <c r="AF2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG2" s="3" t="n">
         <v>132678827</v>
       </c>
-      <c r="AF2" s="2" t="n">
+      <c r="AH2" s="3" t="n">
         <v>98715002</v>
       </c>
-      <c r="AG2" s="2" t="n">
+      <c r="AI2" s="3" t="n">
         <v>97981970.06500001</v>
       </c>
     </row>
@@ -782,121 +810,131 @@
           <t>I. Coast</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>318003</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>31855971</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="F3" s="4" t="n">
         <v>0.0233</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>0.361</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="H3" s="4" t="n">
         <v>0.609</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="I3" s="4" t="n">
         <v>0.03</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>20 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="K3" s="4" t="n">
         <v>0.531</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Akan 38%, Voltaique or Gur 22%, Northern Mande 22%, Kru 9.1%, Southern Mande 8.6%, other 0.3% (2021 est.)</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Muslim 42.9%, Catholic 17.2%, Evangelical 11.8%, Methodist 1.7%, other Christian 3.2%, animist 3.6%, other religion 0.5%, none 19.1% (2014 est.)</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>French (official), 60 native dialects of which Dioula is the most widely spoken</t>
         </is>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="O3" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="P3" s="4" t="n">
         <v>0.602</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="Q3" s="4" t="n">
         <v>0.403</v>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>12 districts</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>$86.538 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="T3" s="4" t="n">
         <v>0.06</v>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>$6,700 (2024 est.)</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>2.3% (2024 est.)</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr">
         <is>
           <t>37,5% (2021 est.)</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>lowest 3.1% (2021 est.)
 highest 27.8% (2021 est.)</t>
         </is>
       </c>
-      <c r="W3" s="2" t="n">
+      <c r="Y3" s="4" t="n">
         <v>0.035</v>
       </c>
-      <c r="X3" s="2" t="n">
+      <c r="Z3" s="3" t="n">
         <v>58700000</v>
       </c>
-      <c r="Y3" s="2" t="n">
+      <c r="AA3" s="4" t="n">
         <v>1.842668678973873</v>
       </c>
-      <c r="Z3" s="2" t="n">
+      <c r="AB3" s="3" t="n">
         <v>13060948.11</v>
       </c>
-      <c r="AA3" s="2" t="n">
+      <c r="AC3" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="AB3" s="2" t="n">
+      <c r="AD3" s="2" t="n">
         <v>178</v>
       </c>
-      <c r="AC3" s="2" t="n">
+      <c r="AE3" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="AD3" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE3" s="2" t="n">
+      <c r="AF3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG3" s="3" t="n">
         <v>16915521</v>
       </c>
-      <c r="AF3" s="2" t="n">
+      <c r="AH3" s="3" t="n">
         <v>11500006</v>
       </c>
-      <c r="AG3" s="2" t="n">
+      <c r="AI3" s="3" t="n">
         <v>11945989.125</v>
       </c>
     </row>
@@ -906,121 +944,131 @@
           <t>Senegal</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>192530</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>18847519</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>0.024</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>0.407</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="H4" s="4" t="n">
         <v>0.5589999999999999</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="I4" s="4" t="n">
         <v>0.034</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>19.4 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="K4" s="4" t="n">
         <v>0.496</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Wolof 39.7%, Pulaar 27.5%, Sereer 16%, Mandinka 4.9%, Jola 4.2%, Soninke 2.4%, other 5.4% (includes Europeans and persons of Lebanese descent) (2019 est.)</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Muslim 97.2% (most adhere to one of the four main Sufi brotherhoods), Christian 2.7% (mostly Roman Catholic) (2019 est.)</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>French (official), Wolof, Pulaar, Jola, Mandinka, Serer, Soninke</t>
         </is>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="O4" s="4" t="n">
         <v>0.504</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="P4" s="4" t="n">
         <v>0.648</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="Q4" s="4" t="n">
         <v>0.398</v>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">14 regions </t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>$32.267 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="T4" s="4" t="n">
         <v>0.06900000000000001</v>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>$4,500 (2024 est.)</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>3% (2024 est.)</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>46.7% (2011 est.)</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 3%
 highest 10%: 28,8% (2021 est.)</t>
         </is>
       </c>
-      <c r="W4" s="2" t="n">
+      <c r="Y4" s="4" t="n">
         <v>0.008</v>
       </c>
-      <c r="X4" s="2" t="n">
+      <c r="Z4" s="3" t="n">
         <v>22400000</v>
       </c>
-      <c r="Y4" s="2" t="n">
+      <c r="AA4" s="4" t="n">
         <v>1.188485338574271</v>
       </c>
-      <c r="Z4" s="2" t="n">
+      <c r="AB4" s="3" t="n">
         <v>11496986.59</v>
       </c>
-      <c r="AA4" s="2" t="n">
+      <c r="AC4" s="4" t="n">
         <v>0.61</v>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AD4" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="AC4" s="2" t="n">
+      <c r="AE4" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="AD4" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE4" s="2" t="n">
+      <c r="AF4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG4" s="3" t="n">
         <v>9348369</v>
       </c>
-      <c r="AF4" s="2" t="n">
+      <c r="AH4" s="3" t="n">
         <v>7670940</v>
       </c>
-      <c r="AG4" s="2" t="n">
+      <c r="AI4" s="3" t="n">
         <v>8801791.373</v>
       </c>
     </row>
@@ -1030,121 +1078,131 @@
           <t>Gambia</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>10120</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>2523327</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="F5" s="4" t="n">
         <v>0.0209</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="G5" s="4" t="n">
         <v>0.382</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="H5" s="4" t="n">
         <v>0.581</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="I5" s="4" t="n">
         <v>0.03700000000000001</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>20.5 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="K5" s="4" t="n">
         <v>0.645</v>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Mandinka/Jahanka 33.3%, Fulani/Tukulur/Lorobo 18.2%, Wolof 12.9%, Jola/Karoninka 11%, Serahuleh 7.2%, Serer 3.5%, other 4%, non-Gambian 9.9% (2019-20 est.)</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Muslim 96.4%, Christian 3.5%, other or none 0.1% (2019-20 est.)</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>English (official), Mandinka, Wolof, Fula, other indigenous vernaculars</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="O5" s="4" t="n">
         <v>0.516</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="P5" s="4" t="n">
         <v>0.653</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="Q5" s="4" t="n">
         <v>0.405</v>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>5 regions</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>$2.508 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="T5" s="4" t="n">
         <v>0.057</v>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>$3,000 (2024 est.)</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>6.5% (2024 est.)</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr">
         <is>
           <t>53.4% (2020 est.)</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2,6%
 highest 10%: 30,5% (2003)</t>
         </is>
       </c>
-      <c r="W5" s="2" t="n">
+      <c r="Y5" s="4" t="n">
         <v>0.116</v>
       </c>
-      <c r="X5" s="2" t="n">
+      <c r="Z5" s="3" t="n">
         <v>2680000</v>
       </c>
-      <c r="Y5" s="2" t="n">
+      <c r="AA5" s="4" t="n">
         <v>1.062089852008876</v>
       </c>
-      <c r="Z5" s="2" t="n">
+      <c r="AB5" s="3" t="n">
         <v>1160730.42</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AC5" s="4" t="n">
         <v>0.46</v>
       </c>
-      <c r="AB5" s="2" t="n">
+      <c r="AD5" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="AC5" s="2" t="n">
+      <c r="AE5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AD5" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE5" s="2" t="n">
+      <c r="AF5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG5" s="3" t="n">
         <v>1627546</v>
       </c>
-      <c r="AF5" s="2" t="n">
+      <c r="AH5" s="3" t="n">
         <v>963911</v>
       </c>
-      <c r="AG5" s="2" t="n">
+      <c r="AI5" s="3" t="n">
         <v>1347456.618</v>
       </c>
     </row>
@@ -1154,121 +1212,131 @@
           <t>Guinea Bissau</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>28120</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>2132325</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="F6" s="4" t="n">
         <v>0.0255</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="G6" s="4" t="n">
         <v>0.423</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="H6" s="4" t="n">
         <v>0.546</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="I6" s="4" t="n">
         <v>0.031</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>18.5 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="K6" s="4" t="n">
         <v>0.455</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Balanta 30%, Fulani 30%, Manjaco 14%, Mandinga 13%, Papel 7%, unspecified smaller ethnic groups 6% (2015 est.)</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>Muslim 46.1%, folk religions 30.6%, Christian 18.9%, other or unaffiliated 4.4% (2020 est.)</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Portuguese-based Creole, Portuguese (official; largely used as a second or third language), Pular (a Fula language), Mandingo</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="O6" s="4" t="n">
         <v>0.639</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="P6" s="4" t="n">
         <v>0.773</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="Q6" s="4" t="n">
         <v>0.522</v>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>9 regions</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>$2.12 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="T6" s="4" t="n">
         <v>0.048</v>
       </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>$2,700 (2024 est.)</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>2.7% (2024 est.)</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>50.5% (2021 est.)</t>
         </is>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 3,4%
 highest 10%: 26.1% (2021 est.)</t>
         </is>
       </c>
-      <c r="W6" s="2" t="n">
+      <c r="Y6" s="4" t="n">
         <v>0.038</v>
       </c>
-      <c r="X6" s="2" t="n">
+      <c r="Z6" s="3" t="n">
         <v>2760000</v>
       </c>
-      <c r="Y6" s="2" t="n">
+      <c r="AA6" s="4" t="n">
         <v>1.294361788188949</v>
       </c>
-      <c r="Z6" s="2" t="n">
+      <c r="AB6" s="3" t="n">
         <v>703667.25</v>
       </c>
-      <c r="AA6" s="2" t="n">
+      <c r="AC6" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="AB6" s="2" t="n">
+      <c r="AD6" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="AC6" s="2" t="n">
+      <c r="AE6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AD6" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE6" s="2" t="n">
+      <c r="AF6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG6" s="3" t="n">
         <v>970208</v>
       </c>
-      <c r="AF6" s="2" t="n">
+      <c r="AH6" s="3" t="n">
         <v>901973</v>
       </c>
-      <c r="AG6" s="2" t="n">
+      <c r="AI6" s="3" t="n">
         <v>1076824.125</v>
       </c>
     </row>
@@ -1278,121 +1346,131 @@
           <t>Sierra Leone</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>71620</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <v>9331203</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="F7" s="4" t="n">
         <v>0.0224</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>0.401</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="H7" s="4" t="n">
         <v>0.574</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="I7" s="4" t="n">
         <v>0.025</v>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>19.7 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="K7" s="4" t="n">
         <v>0.4429999999999999</v>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Temne 35.4%, Mende 30.8%, Limba 8.8%, Kono 4.3%, Korankoh 4%, Fullah 3.8%, Mandingo 2.8%, Loko 2%, Sherbro 1.9%, Creole 1.2% (descendants of freed Jamaican slaves who were settled in the Freetown area in the late-18th century; also known as Krio), other 5% (2019 est.)</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>Muslim 77.1%, Christian 22.9% (2019 est.)</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>English (official, regular use limited to literate minority), Mende (principal vernacular in the south), Temne (principal vernacular in the north), Krio (English-based Creole, spoken by the descendants of freed Jamaican slaves; a first language for 10% of the population but understood by 95%)</t>
         </is>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="O7" s="4" t="n">
         <v>0.436</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="P7" s="4" t="n">
         <v>0.546</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="Q7" s="4" t="n">
         <v>0.339</v>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">4 provinces </t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>$7.548 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="T7" s="4" t="n">
         <v>0.04</v>
       </c>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>$3,100 (2024 est.)</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>3.2% (2024 est.)</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr">
+      <c r="W7" s="2" t="inlineStr">
         <is>
           <t>56.8% (2018 est.)</t>
         </is>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 3,4%
 highest 10%: 29,4% (2018 est.)</t>
         </is>
       </c>
-      <c r="W7" s="2" t="n">
+      <c r="Y7" s="4" t="n">
         <v>0.286</v>
       </c>
-      <c r="X7" s="2" t="n">
+      <c r="Z7" s="3" t="n">
         <v>8930000</v>
       </c>
-      <c r="Y7" s="2" t="n">
+      <c r="AA7" s="4" t="n">
         <v>0.9570041504830621</v>
       </c>
-      <c r="Z7" s="2" t="n">
+      <c r="AB7" s="3" t="n">
         <v>1959552.63</v>
       </c>
-      <c r="AA7" s="2" t="n">
+      <c r="AC7" s="4" t="n">
         <v>0.21</v>
       </c>
-      <c r="AB7" s="2" t="n">
+      <c r="AD7" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="AC7" s="2" t="n">
+      <c r="AE7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AD7" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE7" s="2" t="n">
+      <c r="AF7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG7" s="3" t="n">
         <v>4133723</v>
       </c>
-      <c r="AF7" s="2" t="n">
+      <c r="AH7" s="3" t="n">
         <v>3741812</v>
       </c>
-      <c r="AG7" s="2" t="n">
+      <c r="AI7" s="3" t="n">
         <v>5300123.304</v>
       </c>
     </row>
@@ -1402,121 +1480,131 @@
           <t>Liberia</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>96320</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="E8" s="3" t="n">
         <v>5563541</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="F8" s="4" t="n">
         <v>0.0227</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>0.389</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="H8" s="4" t="n">
         <v>0.579</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="I8" s="4" t="n">
         <v>0.032</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>20.1 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="K8" s="4" t="n">
         <v>0.536</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Kpelle 20.2%, Bassa 13.6%, Grebo 9.9%, Gio 7.9%, Mano 7.2%, Kru 5.5%, Lorma 4.8%, Krahn 4.5%, Kissi, 4.3%, Mandingo 4.2%, Vai 3.8%, Gola 3.8%, Gbandi 2.9%, Mende 1.7%, Sapo 1%, Belle 0.7%, Dey 0.3%, other Liberian ethnic group 0.4%, other African 3%, non-African 0.2% (2022 est.)</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Christian 84.9%, Muslim 12%, Traditional 0.5%, other 0.1%, none 2.6% (2022 est.)</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>English 20% (official) and 27 indigenous languages, including Liberian English variants</t>
         </is>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="O8" s="4" t="n">
         <v>0.483</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="P8" s="4" t="n">
         <v>0.627</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="Q8" s="4" t="n">
         <v>0.341</v>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>15 counties</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>$4.75 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="T8" s="4" t="n">
         <v>0.048</v>
       </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>$1,700 (2024 est.)</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>2.9% (2024 est.)</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>50.9% (2016 est.)</t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2.4%
 highest 10%: 30.1% (2007)</t>
         </is>
       </c>
-      <c r="W8" s="2" t="n">
+      <c r="Y8" s="4" t="n">
         <v>0.124</v>
       </c>
-      <c r="X8" s="2" t="n">
+      <c r="Z8" s="3" t="n">
         <v>2793316</v>
       </c>
-      <c r="Y8" s="2" t="n">
+      <c r="AA8" s="4" t="n">
         <v>0.5020752071387629</v>
       </c>
-      <c r="Z8" s="2" t="n">
+      <c r="AB8" s="3" t="n">
         <v>383819</v>
       </c>
-      <c r="AA8" s="2" t="n">
+      <c r="AC8" s="4" t="n">
         <v>0.06898825765820725</v>
       </c>
-      <c r="AB8" s="2" t="n">
+      <c r="AD8" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="AC8" s="2" t="n">
+      <c r="AE8" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="AD8" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE8" s="2" t="n">
+      <c r="AF8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG8" s="3" t="n">
         <v>2982058</v>
       </c>
-      <c r="AF8" s="2" t="n">
+      <c r="AH8" s="3" t="n">
         <v>2164217</v>
       </c>
-      <c r="AG8" s="2" t="n">
+      <c r="AI8" s="3" t="n">
         <v>2831842.369</v>
       </c>
     </row>
@@ -1526,121 +1614,131 @@
           <t>Guinea Conakry</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
         <v>245717</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="E9" s="3" t="n">
         <v>14374590</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="F9" s="4" t="n">
         <v>0.0274</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="G9" s="4" t="n">
         <v>0.409</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="H9" s="4" t="n">
         <v>0.551</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="I9" s="4" t="n">
         <v>0.04</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>19.5 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="K9" s="4" t="n">
         <v>0.381</v>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Fulani (Peuhl) 33.4%, Malinke 29.4%, Susu 21.2%, Guerze 7.8%, Kissi 6.2%, Toma 1.6%, other/foreign 0.4% (2018 est.)</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>Muslim 85.2%, Christian 13.4%, animist 0.2%, none 1.2% (2018 est.)</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>French (official), Pular, Maninka, Susu, other native languages</t>
         </is>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="O9" s="4" t="n">
         <v>0.396</v>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="P9" s="4" t="n">
         <v>0.544</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="Q9" s="4" t="n">
         <v>0.277</v>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>7 regions</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>$25.334 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R9" s="2" t="n">
+      <c r="T9" s="4" t="n">
         <v>0.057</v>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>$4,000 (2024 est.)</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>5.3% (2024 est.)</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>43,7% (2018 est.)</t>
         </is>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 67,4%
 highest 10%: 13,4% (2024 est.)</t>
         </is>
       </c>
-      <c r="W9" s="2" t="n">
+      <c r="Y9" s="4" t="n">
         <v>0.081</v>
       </c>
-      <c r="X9" s="2" t="n">
+      <c r="Z9" s="3" t="n">
         <v>15300000</v>
       </c>
-      <c r="Y9" s="2" t="n">
+      <c r="AA9" s="4" t="n">
         <v>1.064378184003857</v>
       </c>
-      <c r="Z9" s="2" t="n">
+      <c r="AB9" s="3" t="n">
         <v>3881139.3</v>
       </c>
-      <c r="AA9" s="2" t="n">
+      <c r="AC9" s="4" t="n">
         <v>0.27</v>
       </c>
-      <c r="AB9" s="2" t="n">
+      <c r="AD9" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AC9" s="2" t="n">
+      <c r="AE9" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AD9" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE9" s="2" t="n">
+      <c r="AF9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG9" s="3" t="n">
         <v>5476719</v>
       </c>
-      <c r="AF9" s="2" t="n">
+      <c r="AH9" s="3" t="n">
         <v>5879207</v>
       </c>
-      <c r="AG9" s="2" t="n">
+      <c r="AI9" s="3" t="n">
         <v>6281695.83</v>
       </c>
     </row>
@@ -1650,121 +1748,131 @@
           <t>Burkina Faso</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
         <v>273800</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="E10" s="3" t="n">
         <v>23490300</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="F10" s="4" t="n">
         <v>0.0239</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="G10" s="4" t="n">
         <v>0.416</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="H10" s="4" t="n">
         <v>0.551</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="I10" s="4" t="n">
         <v>0.032</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>19 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="K10" s="4" t="n">
         <v>0.325</v>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Mossi 53.7%, Fulani (Peuhl) 6.8%, Gurunsi 5.9%, Bissa 5.4%, Gurma 5.2%, Bobo 3.4%, Senufo 2.2%, Bissa 1.5%, Lobi 1.5%, Tuareg/Bella 0.1%, other 12.8%, foreign 0.7% (2021 est.)</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>Muslim 63.8%, Roman Catholic 20.1%, Animiste 9%, Protestant 6.2%, other 0.2%, none 0.7% (2019 est.)</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>Mossi 52.9%, Fula 7.8%, Gourmantche 6.8%, Dyula 5.7%, Bissa 3.3%, Gurunsi 3.2%, French (official) 2.2%, Bwamu 2%, Dagara 2%, San 1.7%, Marka 1.6%, Bobo 1.5%, Senufo 1.5%, Lobi 1.2%, other 6.6% (2019 est.)</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="O10" s="4" t="n">
         <v>0.414</v>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="P10" s="4" t="n">
         <v>0.501</v>
       </c>
-      <c r="O10" s="2" t="n">
+      <c r="Q10" s="4" t="n">
         <v>0.327</v>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>13 regions</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>$23.25 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R10" s="2" t="n">
+      <c r="T10" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="S10" s="2" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>$2,500 (2024 est.)</t>
         </is>
       </c>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>5.2% (2024 est.)</t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr">
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>43,2% (2021 est.)</t>
         </is>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2.9%
 highest 10%: 32.2% (2009 est.)</t>
         </is>
       </c>
-      <c r="W10" s="2" t="n">
+      <c r="Y10" s="4" t="n">
         <v>0.042</v>
       </c>
-      <c r="X10" s="2" t="n">
+      <c r="Z10" s="3" t="n">
         <v>20364508</v>
       </c>
-      <c r="Y10" s="2" t="n">
+      <c r="AA10" s="4" t="n">
         <v>0.8669326487954603</v>
       </c>
-      <c r="Z10" s="2" t="n">
+      <c r="AB10" s="3" t="n">
         <v>3158834</v>
       </c>
-      <c r="AA10" s="2" t="n">
+      <c r="AC10" s="4" t="n">
         <v>0.1344739743638864</v>
       </c>
-      <c r="AB10" s="2" t="n">
+      <c r="AD10" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="AC10" s="2" t="n">
+      <c r="AE10" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="AD10" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE10" s="2" t="n">
+      <c r="AF10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG10" s="3" t="n">
         <v>7634348</v>
       </c>
-      <c r="AF10" s="2" t="n">
+      <c r="AH10" s="3" t="n">
         <v>9771965</v>
       </c>
-      <c r="AG10" s="2" t="n">
+      <c r="AI10" s="3" t="n">
         <v>10147809.6</v>
       </c>
     </row>
@@ -1774,123 +1882,133 @@
           <t>Mali</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
         <v>1220190</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="E11" s="3" t="n">
         <v>22634423</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="F11" s="4" t="n">
         <v>0.0288</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="G11" s="4" t="n">
         <v>0.468</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="H11" s="4" t="n">
         <v>0.501</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="I11" s="4" t="n">
         <v>0.031</v>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>16.5 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="K11" s="4" t="n">
         <v>0.462</v>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Bambara 33.3%, Fulani (Peuhl) 13.3%, Sarakole/Soninke/Marka 9.8%, Senufo/Manianka 9.6%, Malinke 8.8%, Dogon 8.7%, Sonrai 5.9%, Bobo 2.1%, Tuareg/Bella 1.7%, other Malian 6%, from members of Economic Community of West Africa 0.4%, other 0.3% (2018 est.)</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Muslim 93.9%, Christian 2.8%, animist 0.7%, none 2.5% (2018 est.)</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>Bambara (official), French 17.2%, Peuhl/Foulfoulbe/Fulani 9.4%, Dogon 7.2%, Maraka/Soninke 6.4%, Malinke 5.6%, Sonrhai/Djerma 5.6%, Minianka 4.3%, Tamacheq 3.5%, Senoufo 2.6%, Bobo 2.1%, other 6.3%, unspecified 0.7% (2009 est.)</t>
         </is>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="O11" s="4" t="n">
         <v>0.355</v>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="P11" s="4" t="n">
         <v>0.462</v>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">25.7% </t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>10 regions</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>$26.588 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R11" s="2" t="n">
+      <c r="T11" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>$2,900 (2024 est.)</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>3.1% (2024 est.)</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>44.6% (2021 est.)</t>
         </is>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 3.5%
 highest 10%: 25.8% (2010 est.)</t>
         </is>
       </c>
-      <c r="W11" s="2" t="n">
+      <c r="Y11" s="4" t="n">
         <v>0.032</v>
       </c>
-      <c r="X11" s="2" t="n">
+      <c r="Z11" s="3" t="n">
         <v>22925482</v>
       </c>
-      <c r="Y11" s="2" t="n">
+      <c r="AA11" s="4" t="n">
         <v>1.012859130537589</v>
       </c>
-      <c r="Z11" s="2" t="n">
+      <c r="AB11" s="3" t="n">
         <v>2395886</v>
       </c>
-      <c r="AA11" s="2" t="n">
+      <c r="AC11" s="4" t="n">
         <v>0.1058514281543647</v>
       </c>
-      <c r="AB11" s="2" t="n">
+      <c r="AD11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AC11" s="2" t="n">
+      <c r="AE11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AD11" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE11" s="2" t="n">
+      <c r="AF11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG11" s="3" t="n">
         <v>10457103</v>
       </c>
-      <c r="AF11" s="2" t="n">
+      <c r="AH11" s="3" t="n">
         <v>10592910</v>
       </c>
-      <c r="AG11" s="2" t="n">
+      <c r="AI11" s="3" t="n">
         <v>10094952.658</v>
       </c>
     </row>
@@ -1902,121 +2020,131 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1,266,700 </t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="E12" s="3" t="n">
         <v>27322555</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="F12" s="4" t="n">
         <v>0.0365</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="G12" s="4" t="n">
         <v>0.495</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="H12" s="4" t="n">
         <v>0.478</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="I12" s="4" t="n">
         <v>0.027</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>15.3 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="K12" s="4" t="n">
         <v>0.171</v>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Hausa 53.1%, Zarma/Songhai 21.2%, Tuareg 11%, Fulani (Peuhl) 6.5%, Kanuri 5.9%, Gurma 0.8%, Arab 0.4%, Tubu 0.4%, other/unavailable 0.9% (2006 est.)</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Muslim 95.5%, ethnic religionist 4.1%, Christian 0.3%, agnostics and other 0.1% (2020 est.)</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>Hausa, Zarma, French (official), Fufulde, Tamashek, Kanuri, Gurmancema, Tagdal</t>
         </is>
       </c>
-      <c r="M12" s="2" t="n">
+      <c r="O12" s="4" t="n">
         <v>0.356</v>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="P12" s="4" t="n">
         <v>0.273</v>
       </c>
-      <c r="O12" s="2" t="n">
+      <c r="Q12" s="4" t="n">
         <v>0.11</v>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>7 regions</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>$19.538 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R12" s="2" t="n">
+      <c r="T12" s="4" t="n">
         <v>0.08400000000000001</v>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>$1,800 (2024 est.)</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0.4% (2024 est.)</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>45.5% (2021 est.)</t>
         </is>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 3.2%
 highest 10%: 26.8% (2014)</t>
         </is>
       </c>
-      <c r="W12" s="2" t="n">
+      <c r="Y12" s="4" t="n">
         <v>0.091</v>
       </c>
-      <c r="X12" s="2" t="n">
+      <c r="Z12" s="3" t="n">
         <v>8921769</v>
       </c>
-      <c r="Y12" s="2" t="n">
+      <c r="AA12" s="4" t="n">
         <v>0.326534945212847</v>
       </c>
-      <c r="Z12" s="2" t="n">
+      <c r="AB12" s="3" t="n">
         <v>1110778</v>
       </c>
-      <c r="AA12" s="2" t="n">
+      <c r="AC12" s="4" t="n">
         <v>0.04065425067311604</v>
       </c>
-      <c r="AB12" s="2" t="n">
+      <c r="AD12" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="AC12" s="2" t="n">
+      <c r="AE12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AD12" s="2" t="n">
+      <c r="AF12" s="2" t="n">
         <v>27322555</v>
       </c>
-      <c r="AE12" s="2" t="n">
+      <c r="AG12" s="3" t="n">
         <v>4672157</v>
       </c>
-      <c r="AF12" s="2" t="n">
+      <c r="AH12" s="3" t="n">
         <v>13524665</v>
       </c>
-      <c r="AG12" s="2" t="n">
+      <c r="AI12" s="3" t="n">
         <v>12431762.525</v>
       </c>
     </row>
@@ -2026,121 +2154,131 @@
           <t>Chad</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
         <v>1259200</v>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="E13" s="3" t="n">
         <v>19674004</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="F13" s="4" t="n">
         <v>0.0298</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="G13" s="4" t="n">
         <v>0.458</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="H13" s="4" t="n">
         <v>0.517</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="I13" s="4" t="n">
         <v>0.025</v>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>16.9 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="K13" s="4" t="n">
         <v>0.244</v>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>Sara (Ngambaye/Sara/Madjingaye/Mbaye) 30.5%, Kanembu/Bornu/Buduma 9.8%, Arab 9.7%, Wadai/Maba/Masalit/Mimi 7%, Gorane 5.8%, Masa/Musseye/Musgum 4.9%, Bulala/Medogo/Kuka 3.7%, Marba/Lele/Mesme 3.5%, Mundang 2.7%, Bidiyo/Migaama/Kenga/Dangleat 2.5%, Dadjo/Kibet/Muro 2.4%, Tupuri/Kera 2%, Gabri/Kabalaye/Nanchere/Somrai 2%, Fulani/Fulbe/Bodore 1.8%, Karo/Zime/Peve 1.3%, Baguirmi/Barma 1.2%, Zaghawa/Bideyat/Kobe 1.1%, Tama/Assongori/Mararit 1.1%, Mesmedje/Massalat/Kadjakse 0.8%, other&amp;nbsp; 4.6%, unspecified 1.7% (2014-15 est.)</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Muslim 52.1%, Protestant 23.9%, Roman Catholic 20%, animist 0.3%, other Christian 0.2%, none 2.8%, unspecified 0.7% (2014-15 est.)</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>French (official), Arabic (official), Sara (in south), more than 120 different languages and dialects</t>
         </is>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="O13" s="4" t="n">
         <v>0.306</v>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="P13" s="4" t="n">
         <v>0.313</v>
       </c>
-      <c r="O13" s="2" t="n">
+      <c r="Q13" s="4" t="n">
         <v>0.14</v>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>23 regions</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>$20.626 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R13" s="2" t="n">
+      <c r="T13" s="4" t="n">
         <v>0.03700000000000001</v>
       </c>
-      <c r="S13" s="2" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>$2,600 (2024 est.)</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>1.1% (2024 est.)</t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr">
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>44.8% (2022 est.)</t>
         </is>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="X13" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2.6%
 highest 10%: 30.8% (2003)</t>
         </is>
       </c>
-      <c r="W13" s="2" t="n">
+      <c r="Y13" s="4" t="n">
         <v>0.08900000000000001</v>
       </c>
-      <c r="X13" s="2" t="n">
+      <c r="Z13" s="3" t="n">
         <v>7664839</v>
       </c>
-      <c r="Y13" s="2" t="n">
+      <c r="AA13" s="4" t="n">
         <v>0.3895922253548388</v>
       </c>
-      <c r="Z13" s="2" t="n">
+      <c r="AB13" s="3" t="n">
         <v>1029153</v>
       </c>
-      <c r="AA13" s="2" t="n">
+      <c r="AC13" s="4" t="n">
         <v>0.05231029738532126</v>
       </c>
-      <c r="AB13" s="2" t="n">
+      <c r="AD13" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="AC13" s="2" t="n">
+      <c r="AE13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AD13" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE13" s="2" t="n">
+      <c r="AF13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG13" s="3" t="n">
         <v>4800457</v>
       </c>
-      <c r="AF13" s="2" t="n">
+      <c r="AH13" s="3" t="n">
         <v>9010694</v>
       </c>
-      <c r="AG13" s="2" t="n">
+      <c r="AI13" s="3" t="n">
         <v>8813953.791999999</v>
       </c>
     </row>
@@ -2150,121 +2288,131 @@
           <t>Cape Verde</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
         <v>4033</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="E14" s="3" t="n">
         <v>611014</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="F14" s="4" t="n">
         <v>0.0112</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="G14" s="4" t="n">
         <v>0.264</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="H14" s="4" t="n">
         <v>0.672</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="I14" s="4" t="n">
         <v>0.064</v>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>29.3 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="K14" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Creole (Mulatto) 71%, African 28%, European 1%</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>Roman Catholic 72.5%, Protestant 4% (includes Adventist 1.9%, Nazarene 1.8%, Assembly of God 0.2%, God is Love 0.1%), Christian Rationalism 1.7%, Muslim 1.3%, Jehovah's Witness 1.2%, Church of Jesus Christ 1%, other Christian 1.3%, other 1.2%, none 15.6%, no response 0.4% (2021 est.)</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>Portuguese (official), Crioulo (a Portuguese-based creole language with two main dialects)</t>
         </is>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="O14" s="4" t="n">
         <v>0.885</v>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="P14" s="4" t="n">
         <v>0.917</v>
       </c>
-      <c r="O14" s="2" t="n">
+      <c r="Q14" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>22 municipalities</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>$2.768 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R14" s="2" t="n">
+      <c r="T14" s="4" t="n">
         <v>0.073</v>
       </c>
-      <c r="S14" s="2" t="inlineStr">
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>$9,900 (2024 est.)</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>11.9% (2024 est.)</t>
         </is>
       </c>
-      <c r="U14" s="2" t="inlineStr">
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>35.2% (2015 est.)</t>
         </is>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 1.9%
 highest 10%: 40.6% (2000)</t>
         </is>
       </c>
-      <c r="W14" s="2" t="n">
+      <c r="Y14" s="4" t="n">
         <v>0.01</v>
       </c>
-      <c r="X14" s="2" t="n">
+      <c r="Z14" s="3" t="n">
         <v>595681</v>
       </c>
-      <c r="Y14" s="2" t="n">
+      <c r="AA14" s="4" t="n">
         <v>0.9749056486430753</v>
       </c>
-      <c r="Z14" s="2" t="n">
+      <c r="AB14" s="3" t="n">
         <v>330623</v>
       </c>
-      <c r="AA14" s="2" t="n">
+      <c r="AC14" s="4" t="n">
         <v>0.5411054411191888</v>
       </c>
-      <c r="AB14" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AC14" s="2" t="n">
-        <v/>
-      </c>
       <c r="AD14" s="2" t="n">
         <v/>
       </c>
       <c r="AE14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AF14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG14" s="3" t="n">
         <v>415490</v>
       </c>
-      <c r="AF14" s="2" t="n">
+      <c r="AH14" s="3" t="n">
         <v>161308</v>
       </c>
-      <c r="AG14" s="2" t="n">
+      <c r="AI14" s="3" t="n">
         <v>215076.928</v>
       </c>
     </row>
@@ -2274,121 +2422,131 @@
           <t>Togo</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
         <v>54385</v>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="E15" s="3" t="n">
         <v>9143439</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="F15" s="4" t="n">
         <v>0.0237</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="G15" s="4" t="n">
         <v>0.387</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="H15" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="I15" s="4" t="n">
         <v>0.043</v>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>20.9 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="K15" s="4" t="n">
         <v>0.445</v>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Adja-Ewe/Mina 42.4%, Kabye/Tem 25.9%, Para-Gourma/Akan 17.1%, Akposso/Akebu 4.1%, Ana-Ife 3.2%, other Togolese 1.7%, foreigners 5.2%, no response 0.4% (2013-14 est.)</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>Christian 42.3%, folk religion 36.9%, Muslim 14%, Hindu &amp;lt;1%, Buddhist &amp;lt;1%, Jewish &amp;lt;1%, other &amp;lt;1%, none 6.2% (2020 est.)</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>French (official, language of commerce), Ewe and Mina (in the south), Kabye (sometimes spelled Kabiye) and Dagomba (in the north)</t>
         </is>
       </c>
-      <c r="M15" s="2" t="n">
+      <c r="O15" s="4" t="n">
         <v>0.726</v>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="P15" s="4" t="n">
         <v>0.773</v>
       </c>
-      <c r="O15" s="2" t="n">
+      <c r="Q15" s="4" t="n">
         <v>0.512</v>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>5 regions</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>$9.926 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R15" s="2" t="n">
+      <c r="T15" s="4" t="n">
         <v>0.053</v>
       </c>
-      <c r="S15" s="2" t="inlineStr">
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>$2,800 (2024 est.)</t>
         </is>
       </c>
-      <c r="T15" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>2% (2024 est.)</t>
         </is>
       </c>
-      <c r="U15" s="2" t="inlineStr">
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>45.5% (2018 est.)</t>
         </is>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="X15" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 3.3%
 highest 10%: 27.1% (2006)</t>
         </is>
       </c>
-      <c r="W15" s="2" t="n">
+      <c r="Y15" s="4" t="n">
         <v>0.029</v>
       </c>
-      <c r="X15" s="2" t="n">
+      <c r="Z15" s="3" t="n">
         <v>6239183</v>
       </c>
-      <c r="Y15" s="2" t="n">
+      <c r="AA15" s="4" t="n">
         <v>0.6823672143489993</v>
       </c>
-      <c r="Z15" s="2" t="n">
+      <c r="AB15" s="3" t="n">
         <v>1010609</v>
       </c>
-      <c r="AA15" s="2" t="n">
+      <c r="AC15" s="4" t="n">
         <v>0.1105283252832988</v>
       </c>
-      <c r="AB15" s="2" t="n">
+      <c r="AD15" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AC15" s="2" t="n">
+      <c r="AE15" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AD15" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE15" s="2" t="n">
+      <c r="AF15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG15" s="3" t="n">
         <v>4068830</v>
       </c>
-      <c r="AF15" s="2" t="n">
+      <c r="AH15" s="3" t="n">
         <v>3538511</v>
       </c>
-      <c r="AG15" s="2" t="n">
+      <c r="AI15" s="3" t="n">
         <v>4160264.745</v>
       </c>
     </row>
@@ -2400,123 +2558,133 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">110,622 </t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="E16" s="3" t="n">
         <v>15186090</v>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="F16" s="4" t="n">
         <v>0.0326</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="G16" s="4" t="n">
         <v>0.453</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="H16" s="4" t="n">
         <v>0.522</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="I16" s="4" t="n">
         <v>0.025</v>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>17.2 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="K16" s="4" t="n">
         <v>0.501</v>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Fon and related 38.4%, Adja and related 15.1%, Yoruba and related 12%, Bariba and related 9.6%, Fulani and related 8.6%, Ottamari and related 6.1%, Yoa-Lokpa and related 4.3%, Dendi and related 2.9%, other 0.9%, foreigner 1.9% (2013 est.)</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>Muslim 27.7%, Roman Catholic 25.5%, Protestant 13.5% (Celestial 6.7%, Methodist 3.4%, other Protestant 3.4%), Vodoun 11.6%, other Christian 9.5%, other traditional religions 2.6%, other 2.6%, none 5.8% (2013 est.)</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>55 languages; French (official); Fon (a Gbe language), Yom (a Gur language) and Yoruba are the most important indigenous languages in the south; half a dozen regionally important languages in the north, including Bariba and Fulfulde</t>
         </is>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="O16" s="4" t="n">
         <v>0.514</v>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="P16" s="4" t="n">
         <v>0.54</v>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">31.1% </t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>12 departments</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>$21.483 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R16" s="2" t="n">
+      <c r="T16" s="4" t="n">
         <v>0.075</v>
       </c>
-      <c r="S16" s="2" t="inlineStr">
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>$3,900 (2024 est.)</t>
         </is>
       </c>
-      <c r="T16" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>1.8% (2024 est.)</t>
         </is>
       </c>
-      <c r="U16" s="2" t="inlineStr">
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>38.5% (2019 est.)</t>
         </is>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 3.1%
 highest 10%: 29% (2003)</t>
         </is>
       </c>
-      <c r="W16" s="2" t="n">
+      <c r="Y16" s="4" t="n">
         <v>0.012</v>
       </c>
-      <c r="X16" s="2" t="n">
+      <c r="Z16" s="3" t="n">
         <v>10349847</v>
       </c>
-      <c r="Y16" s="2" t="n">
+      <c r="AA16" s="4" t="n">
         <v>0.681534680750608</v>
       </c>
-      <c r="Z16" s="2" t="n">
+      <c r="AB16" s="3" t="n">
         <v>2403596</v>
       </c>
-      <c r="AA16" s="2" t="n">
+      <c r="AC16" s="4" t="n">
         <v>0.1582761593010446</v>
       </c>
-      <c r="AB16" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AC16" s="2" t="n">
-        <v/>
-      </c>
       <c r="AD16" s="2" t="n">
         <v/>
       </c>
       <c r="AE16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG16" s="3" t="n">
         <v>7608231</v>
       </c>
-      <c r="AF16" s="2" t="n">
+      <c r="AH16" s="3" t="n">
         <v>6879299</v>
       </c>
-      <c r="AG16" s="2" t="n">
+      <c r="AI16" s="3" t="n">
         <v>5846644.65</v>
       </c>
     </row>
@@ -2526,123 +2694,133 @@
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
         <v>472710</v>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="E17" s="3" t="n">
         <v>31518954</v>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="F17" s="4" t="n">
         <v>0.0237</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="G17" s="4" t="n">
         <v>0.415</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="H17" s="4" t="n">
         <v>0.5529999999999999</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="I17" s="4" t="n">
         <v>0.032</v>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>19.4 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="K17" s="4" t="n">
         <v>0.593</v>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Bamileke-Bamu 22.2%, Biu-Mandara 16.4%, Arab-Choa/Hausa/Kanuri 13.5%, Beti/Bassa, Mbam 13.1%, Grassfields 9.9%, Adamawa-Ubangi, 9.8%, Cotier/Ngoe/Oroko 4.6%, Southwestern Bantu 4.3%, Kako/Meka 2.3%, foreign/other ethnic group 3.8% (2022 est.)</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>Roman Catholic 33.1%, Muslim 30.6%, Protestant 27.1% other Christian 6.1%, animist 1.3%, other 0.7%, none 1.2% (2022 est.)</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>French
 English
 24 major languages</t>
         </is>
       </c>
-      <c r="M17" s="2" t="n">
+      <c r="O17" s="4" t="n">
         <v>0.726</v>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="P17" s="4" t="n">
         <v>0.826</v>
       </c>
-      <c r="O17" s="2" t="n">
+      <c r="Q17" s="4" t="n">
         <v>0.716</v>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>10 regions</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>$51.327 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R17" s="2" t="n">
+      <c r="T17" s="4" t="n">
         <v>0.03700000000000001</v>
       </c>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>$4,900 (2024 est.)</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>3.6% (2024 est.)</t>
         </is>
       </c>
-      <c r="U17" s="2" t="inlineStr">
+      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>37.5% (2014 est.)</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="X17" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 37.5%
 highest 10%: 35.4% (2001)</t>
         </is>
       </c>
-      <c r="W17" s="2" t="n">
+      <c r="Y17" s="4" t="n">
         <v>0.045</v>
       </c>
-      <c r="X17" s="2" t="n">
+      <c r="Z17" s="3" t="n">
         <v>21400736</v>
       </c>
-      <c r="Y17" s="2" t="n">
+      <c r="AA17" s="4" t="n">
         <v>0.6789798925433883</v>
       </c>
-      <c r="Z17" s="2" t="n">
+      <c r="AB17" s="3" t="n">
         <v>6089200</v>
       </c>
-      <c r="AA17" s="2" t="n">
+      <c r="AC17" s="4" t="n">
         <v>0.1931916903079969</v>
       </c>
-      <c r="AB17" s="2" t="n">
+      <c r="AD17" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="AC17" s="2" t="n">
+      <c r="AE17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AD17" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE17" s="2" t="n">
+      <c r="AF17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG17" s="3" t="n">
         <v>18690740</v>
       </c>
-      <c r="AF17" s="2" t="n">
+      <c r="AH17" s="3" t="n">
         <v>13080366</v>
       </c>
-      <c r="AG17" s="2" t="n">
+      <c r="AI17" s="3" t="n">
         <v>11819607.75</v>
       </c>
     </row>
@@ -2652,121 +2830,131 @@
           <t>Gabon</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>257667</v>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="E18" s="3" t="n">
         <v>2513738</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="F18" s="4" t="n">
         <v>0.0235</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="G18" s="4" t="n">
         <v>0.346</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="H18" s="4" t="n">
         <v>0.611</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="I18" s="4" t="n">
         <v>0.043</v>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>22.3 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="K18" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Fang 23.5%, Shira-Punu'Vii 20.6%, Nzabi-Duma 11.2%, Mbede-Teke 5.6%, Myene 4.4%, Kota-Kele 4.3%, Okande-Tsogho 1.6%, other 12.6%, foreigner 16.2% (2021 est.)</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Protestant 46.4% (Revival Church 37%, other Protestant 9.4%), Roman Catholic 29.8%, other Christian 4%, Muslim 10.8%, traditional/animist 1.1%, other 0.9%, none 7% (2019-21 est.)</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>French (official), Fang, Myene, Nzebi, Bapounou/Eschira, Bandjabi</t>
         </is>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="O18" s="4" t="n">
         <v>0.889</v>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="P18" s="4" t="n">
         <v>0.859</v>
       </c>
-      <c r="O18" s="2" t="n">
+      <c r="Q18" s="4" t="n">
         <v>0.834</v>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>9 provinces</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>$20.867 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R18" s="2" t="n">
+      <c r="T18" s="4" t="n">
         <v>0.034</v>
       </c>
-      <c r="S18" s="2" t="inlineStr">
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>$18,900 (2024 est.)</t>
         </is>
       </c>
-      <c r="T18" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>20.1% (2024 est.)</t>
         </is>
       </c>
-      <c r="U18" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>33.4% (2017 est.)</t>
         </is>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2.5%
 highest 10%: 32.7% (2005)</t>
         </is>
       </c>
-      <c r="W18" s="2" t="n">
+      <c r="Y18" s="4" t="n">
         <v>0.012</v>
       </c>
-      <c r="X18" s="2" t="n">
+      <c r="Z18" s="3" t="n">
         <v>2992811</v>
       </c>
-      <c r="Y18" s="2" t="n">
+      <c r="AA18" s="4" t="n">
         <v>1.309814557409651</v>
       </c>
-      <c r="Z18" s="2" t="n">
+      <c r="AB18" s="3" t="n">
         <v>1313802</v>
       </c>
-      <c r="AA18" s="2" t="n">
+      <c r="AC18" s="4" t="n">
         <v>0.5749901965589922</v>
       </c>
-      <c r="AB18" s="2" t="n">
+      <c r="AD18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AC18" s="2" t="n">
+      <c r="AE18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AD18" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE18" s="2" t="n">
+      <c r="AF18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG18" s="3" t="n">
         <v>2287502</v>
       </c>
-      <c r="AF18" s="2" t="n">
+      <c r="AH18" s="3" t="n">
         <v>869753</v>
       </c>
-      <c r="AG18" s="2" t="n">
+      <c r="AI18" s="3" t="n">
         <v>763160.608</v>
       </c>
     </row>
@@ -2776,121 +2964,131 @@
           <t>Congo Brazzaville</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
         <v>341500</v>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="E19" s="3" t="n">
         <v>6097665</v>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="F19" s="4" t="n">
         <v>0.0236</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="G19" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="H19" s="4" t="n">
         <v>0.578</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="I19" s="4" t="n">
         <v>0.043</v>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>20.9 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="K19" s="4" t="n">
         <v>0.6920000000000001</v>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Kongo (Bakongo) 40.5%, Teke 16.9%, Mbochi 13.1%, foreigner 8.2%, Sangha 5.6%, Mbere/Mbeti/Kele 4.4%, Punu 4.3%, Pygmy 1.6%, Oubanguiens 1.6%, Duma 1.5%, Makaa 1.3%, other and unspecified 1% (2014-15 est.)</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>Roman Catholic 33.1%, Awakening Churches/Christian Revival 22.3%, Protestant 19.9%, Salutiste 2.2%, Muslim 1.6%, Kimbanguist 1.5%, other 8.1%, none 11.3% (2007 est.)</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>French (official), French Lingala and Monokutuba (lingua franca trade languages), many local languages and dialects (of which Kikongo is the most widespread)</t>
         </is>
       </c>
-      <c r="M19" s="2" t="n">
+      <c r="O19" s="4" t="n">
         <v>0.803</v>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="P19" s="4" t="n">
         <v>0.861</v>
       </c>
-      <c r="O19" s="2" t="n">
+      <c r="Q19" s="4" t="n">
         <v>0.746</v>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>12 departments</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>$15.72 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R19" s="2" t="n">
+      <c r="T19" s="4" t="n">
         <v>0.026</v>
       </c>
-      <c r="S19" s="2" t="inlineStr">
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>$6,200 (2024 est.)</t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>19.7% (2024 est.)</t>
         </is>
       </c>
-      <c r="U19" s="2" t="inlineStr">
+      <c r="W19" s="2" t="inlineStr">
         <is>
           <t>40.9% (2011 est.)</t>
         </is>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2.1%
 highest 10%: 37.1% (2005)</t>
         </is>
       </c>
-      <c r="W19" s="2" t="n">
+      <c r="Y19" s="4" t="n">
         <v>0.031</v>
       </c>
-      <c r="X19" s="2" t="n">
+      <c r="Z19" s="3" t="n">
         <v>4933529</v>
       </c>
-      <c r="Y19" s="2" t="n">
+      <c r="AA19" s="4" t="n">
         <v>0.9106797080673547</v>
       </c>
-      <c r="Z19" s="2" t="n">
+      <c r="AB19" s="3" t="n">
         <v>437865</v>
       </c>
-      <c r="AA19" s="2" t="n">
+      <c r="AC19" s="4" t="n">
         <v>0.0808254639575266</v>
       </c>
-      <c r="AB19" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AC19" s="2" t="n">
-        <v/>
-      </c>
       <c r="AD19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AF19" s="2" t="n">
         <v>5417414</v>
       </c>
-      <c r="AE19" s="2" t="n">
+      <c r="AG19" s="3" t="n">
         <v>4219584</v>
       </c>
-      <c r="AF19" s="2" t="n">
+      <c r="AH19" s="3" t="n">
         <v>2304917</v>
       </c>
-      <c r="AG19" s="2" t="n">
+      <c r="AI19" s="3" t="n">
         <v>2215722.326</v>
       </c>
     </row>
@@ -2900,119 +3098,129 @@
           <t>Central Africa R.</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>622984</v>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="E20" s="3" t="n">
         <v>5750570</v>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="F20" s="4" t="n">
         <v>0.0174</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="G20" s="4" t="n">
         <v>0.385</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="H20" s="4" t="n">
         <v>0.58</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="I20" s="4" t="n">
         <v>0.035</v>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>20.6 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="K20" s="4" t="n">
         <v>0.436</v>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Baya 28.8%, Banda 22.9%, Mandjia 9.9%, Sara 7.9%, M'Baka-Bantu 7.9%, Arab-Fulani (Peuhl) 6%, Mbum 6%, Ngbanki 5.5%, Zande-Nzakara 3%, other Central African Republic ethnic groups 2%, non-Central African Republic ethnic groups .1% (2003 est.)</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>Roman Catholic 34.6%, Protestant 15.7%, other Christian 22.9%, Muslim 13.8%, ethnic religionist 12%, Baha'i 0.2%, agnostic/atheist 0.7% (2020 est.)</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>French (official), Sangho (lingua franca and national language), tribal languages</t>
         </is>
       </c>
-      <c r="M20" s="2" t="n">
+      <c r="O20" s="4" t="n">
         <v>0.424</v>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="P20" s="4" t="n">
         <v>0.495</v>
       </c>
-      <c r="O20" s="2" t="n">
+      <c r="Q20" s="4" t="n">
         <v>0.258</v>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>14 prefectures</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>$2.752 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R20" s="2" t="n">
+      <c r="T20" s="4" t="n">
         <v>0.015</v>
       </c>
-      <c r="S20" s="2" t="inlineStr">
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>$1,100 (2024 est.)</t>
         </is>
       </c>
-      <c r="T20" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>5.9% (2024 est.)</t>
         </is>
       </c>
-      <c r="U20" s="2" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="W20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2.1%
 highest 10%: 33% (2003)</t>
         </is>
       </c>
-      <c r="W20" s="2" t="n">
+      <c r="Y20" s="4" t="n">
         <v>0.027</v>
       </c>
-      <c r="X20" s="2" t="n">
+      <c r="Z20" s="3" t="n">
         <v>1595294</v>
       </c>
-      <c r="Y20" s="2" t="n">
+      <c r="AA20" s="4" t="n">
         <v>0.2977414639536065</v>
       </c>
-      <c r="Z20" s="2" t="n">
+      <c r="AB20" s="3" t="n">
         <v>249336</v>
       </c>
-      <c r="AA20" s="2" t="n">
+      <c r="AC20" s="4" t="n">
         <v>0.04653541331963664</v>
       </c>
-      <c r="AB20" s="2" t="n">
+      <c r="AD20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AC20" s="2" t="n">
+      <c r="AE20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AD20" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE20" s="2" t="n">
+      <c r="AF20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG20" s="3" t="n">
         <v>2507249</v>
       </c>
-      <c r="AF20" s="2" t="n">
+      <c r="AH20" s="3" t="n">
         <v>2213969</v>
       </c>
-      <c r="AG20" s="2" t="n">
+      <c r="AI20" s="3" t="n">
         <v>2143193.6</v>
       </c>
     </row>
@@ -3022,121 +3230,131 @@
           <t>Ghana</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
         <v>227533</v>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="E21" s="3" t="n">
         <v>35336133</v>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="F21" s="4" t="n">
         <v>0.0212</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="G21" s="4" t="n">
         <v>0.374</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="H21" s="4" t="n">
         <v>0.5820000000000001</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="I21" s="4" t="n">
         <v>0.044</v>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>21.6 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="K21" s="4" t="n">
         <v>0.5920000000000001</v>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Akan 45.7%, Mole-Dagbani 18.5%, Ewe 12.8%, Ga-Dangme 7.1%, Gurma 6.4%, Guan 3.2%, Grusi 2.7%, Mande 2%, other 1.6% (2021 est.)</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>Christian 71.3% (Pentecostal/Charismatic 31.6%, Protestant 17.4%, Catholic 10%, other 12.3%), Muslim 19.9%, traditionalist 3.2%, other 4.5%, none 1.1% (2021 est.)</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>Asante 16%, Ewe 14%, Fante 11.6%, Boron (Brong) 4.9%, Dagomba 4.4%, Dangme 4.2%, Dagarte (Dagaba) 3.9%, Kokomba 3.5%, Akyem 3.2%, Ga 3.1%, other 31.2% (2010 est.)</t>
         </is>
       </c>
-      <c r="M21" s="2" t="n">
+      <c r="O21" s="4" t="n">
         <v>0.765</v>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="P21" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="O21" s="2" t="n">
+      <c r="Q21" s="4" t="n">
         <v>0.714</v>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>16 regions</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>$82.825 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R21" s="2" t="n">
+      <c r="T21" s="4" t="n">
         <v>0.057</v>
       </c>
-      <c r="S21" s="2" t="inlineStr">
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>$7,100 (2024 est.)</t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>3.1% (2024 est.)</t>
         </is>
       </c>
-      <c r="U21" s="2" t="inlineStr">
+      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>23.4% (2016 est.)</t>
         </is>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="X21" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2%
 highest 10%: 32.8% (2006)</t>
         </is>
       </c>
-      <c r="W21" s="2" t="n">
+      <c r="Y21" s="4" t="n">
         <v>0.228</v>
       </c>
-      <c r="X21" s="2" t="n">
+      <c r="Z21" s="3" t="n">
         <v>40857077</v>
       </c>
-      <c r="Y21" s="2" t="n">
+      <c r="AA21" s="4" t="n">
         <v>1.262076949635233</v>
       </c>
-      <c r="Z21" s="2" t="n">
+      <c r="AB21" s="3" t="n">
         <v>10959964</v>
       </c>
-      <c r="AA21" s="2" t="n">
+      <c r="AC21" s="4" t="n">
         <v>0.3385537818388714</v>
       </c>
-      <c r="AB21" s="2" t="n">
+      <c r="AD21" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="AC21" s="2" t="n">
+      <c r="AE21" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AD21" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE21" s="2" t="n">
+      <c r="AF21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG21" s="3" t="n">
         <v>20918991</v>
       </c>
-      <c r="AF21" s="2" t="n">
+      <c r="AH21" s="3" t="n">
         <v>13215714</v>
       </c>
-      <c r="AG21" s="2" t="n">
+      <c r="AI21" s="3" t="n">
         <v>7575256.026000001</v>
       </c>
     </row>
@@ -3146,121 +3364,131 @@
           <t>Namibia</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>823290</v>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="E22" s="3" t="n">
         <v>2852777</v>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="F22" s="4" t="n">
         <v>0.0176</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="G22" s="4" t="n">
         <v>0.341</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="H22" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="I22" s="4" t="n">
         <v>0.039</v>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>23.1 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="K22" s="4" t="n">
         <v>0.5489999999999999</v>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Ovambo 50%, Kavangos 9%, Herero 7%, Damara 7%, mixed European and African ancestry 6.5%, European 6%, Nama 5%, Caprivian 4%, San 3%, Baster 2%, Tswana 0.5%</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>Christian 97.5%, other 0.6% (includes Muslim, Baha'i, Jewish, Buddhist), unaffiliated 1.9% (2020 est.)</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>Oshiwambo languages 49.7%, Nama/Damara 11%, Kavango languages 10.4%, Afrikaans 9.4%, Herero languages 9.2%, Zambezi languages 4.9%, English (official) 2.3%, other African languages 1.5%, other European languages 0.7%, other 1% (2016 est.)</t>
         </is>
       </c>
-      <c r="M22" s="2" t="n">
+      <c r="O22" s="4" t="n">
         <v>0.8759999999999999</v>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="P22" s="4" t="n">
         <v>0.916</v>
       </c>
-      <c r="O22" s="2" t="n">
+      <c r="Q22" s="4" t="n">
         <v>0.914</v>
       </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>14 regions</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>$13.372 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R22" s="2" t="n">
+      <c r="T22" s="4" t="n">
         <v>0.03700000000000001</v>
       </c>
-      <c r="S22" s="2" t="inlineStr">
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>$10,300 (2024 est.)</t>
         </is>
       </c>
-      <c r="T22" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>19.2% (2024 est.)</t>
         </is>
       </c>
-      <c r="U22" s="2" t="inlineStr">
+      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>17.4% (2015 est.)</t>
         </is>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="X22" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2.4%
 highest 10%: 42% (2010)</t>
         </is>
       </c>
-      <c r="W22" s="2" t="n">
+      <c r="Y22" s="4" t="n">
         <v>0.042</v>
       </c>
-      <c r="X22" s="2" t="n">
+      <c r="Z22" s="3" t="n">
         <v>2823655</v>
       </c>
-      <c r="Y22" s="2" t="n">
+      <c r="AA22" s="4" t="n">
         <v>1.054314274075299</v>
       </c>
-      <c r="Z22" s="2" t="n">
+      <c r="AB22" s="3" t="n">
         <v>1291944</v>
       </c>
-      <c r="AA22" s="2" t="n">
+      <c r="AC22" s="4" t="n">
         <v>0.4823942728505921</v>
       </c>
-      <c r="AB22" s="2" t="n">
+      <c r="AD22" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AC22" s="2" t="n">
+      <c r="AE22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AD22" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE22" s="2" t="n">
+      <c r="AF22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG22" s="3" t="n">
         <v>1566175</v>
       </c>
-      <c r="AF22" s="2" t="n">
+      <c r="AH22" s="3" t="n">
         <v>972797</v>
       </c>
-      <c r="AG22" s="2" t="n">
+      <c r="AI22" s="3" t="n">
         <v>466005.234</v>
       </c>
     </row>
@@ -3270,121 +3498,131 @@
           <t>Mozzambique</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
         <v>786380</v>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="E23" s="3" t="n">
         <v>34206144</v>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="F23" s="4" t="n">
         <v>0.0253</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="G23" s="4" t="n">
         <v>0.447</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="H23" s="4" t="n">
         <v>0.524</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="I23" s="4" t="n">
         <v>0.029</v>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>17.4 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="K23" s="4" t="n">
         <v>0.388</v>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>African 99% (Makhuwa, Tsonga, Lomwe, Sena, and others), Mestizo 0.8%, other (includes European, Indian, Pakistani, Chinese) 0.2% (2017 est.)</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>Catholic 27.3%, Islam 19.1%, Pentecostal 16.7%, Saio/Zione 16.3%, no religion 13.5%, other 4.3%, Anglican 1.7%, unknown 1.2% (2017 est.)</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>Makhuwa 26.1%, Portuguese (official) 16.6%, Tsonga 8.6%, Nyanja 8.1, Sena 7.1%, Lomwe 7.1%, Chuwabo 4.7%, Ndau 3.8%, Tswa 3.8%, other Mozambican languages 11.8%, other 0.5%, unspecified 1.8% (2017 est.)</t>
         </is>
       </c>
-      <c r="M23" s="2" t="n">
+      <c r="O23" s="4" t="n">
         <v>0.617</v>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="P23" s="4" t="n">
         <v>0.726</v>
       </c>
-      <c r="O23" s="2" t="n">
+      <c r="Q23" s="4" t="n">
         <v>0.503</v>
       </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>10 provinces</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>$22.417 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R23" s="2" t="n">
+      <c r="T23" s="4" t="n">
         <v>0.019</v>
       </c>
-      <c r="S23" s="2" t="inlineStr">
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>$1,500 (2024 est.)</t>
         </is>
       </c>
-      <c r="T23" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>3.6% (2024 est.)</t>
         </is>
       </c>
-      <c r="U23" s="2" t="inlineStr">
+      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>46.1% (2014 est.)</t>
         </is>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="X23" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 1.9%
 highest 10%: 36.7% (2008)</t>
         </is>
       </c>
-      <c r="W23" s="2" t="n">
+      <c r="Y23" s="4" t="n">
         <v>0.04099999999999999</v>
       </c>
-      <c r="X23" s="2" t="n">
+      <c r="Z23" s="3" t="n">
         <v>14773364</v>
       </c>
-      <c r="Y23" s="2" t="n">
+      <c r="AA23" s="4" t="n">
         <v>0.4782876113125232</v>
       </c>
-      <c r="Z23" s="2" t="n">
+      <c r="AB23" s="3" t="n">
         <v>2855670</v>
       </c>
-      <c r="AA23" s="2" t="n">
+      <c r="AC23" s="4" t="n">
         <v>0.09245230693543008</v>
       </c>
-      <c r="AB23" s="2" t="n">
+      <c r="AD23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AC23" s="2" t="n">
+      <c r="AE23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AD23" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE23" s="2" t="n">
+      <c r="AF23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG23" s="3" t="n">
         <v>13271984</v>
       </c>
-      <c r="AF23" s="2" t="n">
+      <c r="AH23" s="3" t="n">
         <v>15290146</v>
       </c>
-      <c r="AG23" s="2" t="n">
+      <c r="AI23" s="3" t="n">
         <v>14239383.674</v>
       </c>
     </row>
@@ -3396,121 +3634,131 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">581,540 </t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="E24" s="3" t="n">
         <v>31345040</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="F24" s="4" t="n">
         <v>0.0215</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="G24" s="4" t="n">
         <v>0.37</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="H24" s="4" t="n">
         <v>0.591</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="I24" s="4" t="n">
         <v>0.039</v>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>20.5 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="K24" s="4" t="n">
         <v>0.406</v>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>Malayo-Indonesian (Merina and related Betsileo), Cotiers (mixed African, Malayo-Indonesian, and Arab ancestry - Betsimisaraka, Tsimihety, Antaisaka, Sakalava), French, Indian, Creole, Comoran</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>Church of Jesus Christ in Madagascar/Malagasy Lutheran Church/Anglican Church 34%, Roman Catholic 32.3%, other Christian 8.1%, traditional/Animist 1.7%, Muslim 1.4%, other 0.6%, none 21.9% (2021 est.)</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>Malagasy (official) 99.9%, French (official) 23.6%, English 8.2%, other 0.6% (2018 est.)</t>
         </is>
       </c>
-      <c r="M24" s="2" t="n">
+      <c r="O24" s="4" t="n">
         <v>0.747</v>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="P24" s="4" t="n">
         <v>0.773</v>
       </c>
-      <c r="O24" s="2" t="n">
+      <c r="Q24" s="4" t="n">
         <v>0.724</v>
       </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>6 provinces</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>$17.421 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R24" s="2" t="n">
+      <c r="T24" s="4" t="n">
         <v>0.042</v>
       </c>
-      <c r="S24" s="2" t="inlineStr">
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>$1,700 (2024 est.)</t>
         </is>
       </c>
-      <c r="T24" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>3.1% (2024 est.)</t>
         </is>
       </c>
-      <c r="U24" s="2" t="inlineStr">
+      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>70.7% (2012 est.)</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="X24" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2.2%
 highest 10%: 34.7% (2010 est.)</t>
         </is>
       </c>
-      <c r="W24" s="2" t="n">
+      <c r="Y24" s="4" t="n">
         <v>0.056</v>
       </c>
-      <c r="X24" s="2" t="n">
+      <c r="Z24" s="3" t="n">
         <v>10677153</v>
       </c>
-      <c r="Y24" s="2" t="n">
+      <c r="AA24" s="4" t="n">
         <v>0.3877756856035192</v>
       </c>
-      <c r="Z24" s="2" t="n">
+      <c r="AB24" s="3" t="n">
         <v>2516994</v>
       </c>
-      <c r="AA24" s="2" t="n">
+      <c r="AC24" s="4" t="n">
         <v>0.09141285827878874</v>
       </c>
-      <c r="AB24" s="2" t="n">
+      <c r="AD24" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AC24" s="2" t="n">
+      <c r="AE24" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AD24" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE24" s="2" t="n">
+      <c r="AF24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG24" s="3" t="n">
         <v>12726086</v>
       </c>
-      <c r="AF24" s="2" t="n">
+      <c r="AH24" s="3" t="n">
         <v>11597665</v>
       </c>
-      <c r="AG24" s="2" t="n">
+      <c r="AI24" s="3" t="n">
         <v>19466788.278</v>
       </c>
     </row>
@@ -3520,123 +3768,133 @@
           <t>Equatorial Guinea</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
         <v>28051</v>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="E25" s="3" t="n">
         <v>1795834</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="F25" s="4" t="n">
         <v>0.031</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="G25" s="4" t="n">
         <v>0.356</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="H25" s="4" t="n">
         <v>0.594</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="I25" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>22.3 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="K25" s="4" t="n">
         <v>0.7440000000000001</v>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>Fang 78.1%, Bubi 9.4%, Ndowe 2.8%, Nanguedambo 2.7%, Bisio 0.9%, foreigner 5.3%, other 0.7%, unspecified 0.2% (2011 est.)</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>Roman Catholic 88%, Protestant 5%, Muslim 2%, other 5% (animist, Baha'i, Jewish) (2015 est.)</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Spanish (official) 67.6%, other (includes Fang, Bubi, Portuguese (official), French (official), Portuguese-based Creoles spoken in Ano Bom) 32.4% </t>
         </is>
       </c>
-      <c r="M25" s="2" t="n">
+      <c r="O25" s="4" t="n">
         <v>0.953</v>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="P25" s="4" t="n">
         <v>0.974</v>
       </c>
-      <c r="O25" s="2" t="n">
+      <c r="Q25" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>8 provinces</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>$12.766 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R25" s="2" t="n">
+      <c r="T25" s="4" t="n">
         <v>0.009000000000000001</v>
       </c>
-      <c r="S25" s="2" t="inlineStr">
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t>$15,500 (2024 est.)</t>
         </is>
       </c>
-      <c r="T25" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>7.9% (2024 est.)</t>
         </is>
       </c>
-      <c r="U25" s="2" t="inlineStr">
+      <c r="W25" s="2" t="inlineStr">
         <is>
           <t>44% (2011 est.)</t>
         </is>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="X25" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: NA
 highest 10%: NA</t>
         </is>
       </c>
-      <c r="W25" s="2" t="n">
+      <c r="Y25" s="4" t="n">
         <v>0.012</v>
       </c>
-      <c r="X25" s="2" t="n">
+      <c r="Z25" s="3" t="n">
         <v>368920</v>
       </c>
-      <c r="Y25" s="2" t="n">
+      <c r="AA25" s="4" t="n">
         <v>0.4304743946380897</v>
       </c>
-      <c r="Z25" s="2" t="n">
+      <c r="AB25" s="3" t="n">
         <v>209253</v>
       </c>
-      <c r="AA25" s="2" t="n">
+      <c r="AC25" s="4" t="n">
         <v>0.2441669155947202</v>
       </c>
-      <c r="AB25" s="2" t="n">
+      <c r="AD25" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AC25" s="2" t="n">
+      <c r="AE25" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AD25" s="2" t="inlineStr">
+      <c r="AF25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">857008 </t>
         </is>
       </c>
-      <c r="AE25" s="2" t="n">
+      <c r="AG25" s="3" t="n">
         <v>1336100</v>
       </c>
-      <c r="AF25" s="2" t="n">
+      <c r="AH25" s="3" t="n">
         <v>639317</v>
       </c>
-      <c r="AG25" s="2" t="n">
+      <c r="AI25" s="3" t="n">
         <v>377083.52</v>
       </c>
     </row>
@@ -3646,121 +3904,131 @@
           <t>Sao Tome &amp; Principe</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>964</v>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="E26" s="3" t="n">
         <v>223561</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="F26" s="4" t="n">
         <v>0.0139</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="G26" s="4" t="n">
         <v>0.364</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="H26" s="4" t="n">
         <v>0.603</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="I26" s="4" t="n">
         <v>0.032</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>21.2 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="K26" s="4" t="n">
         <v>0.764</v>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Mestico, Angolares (descendants of Angolan slaves), Forros (descendants of freed slaves), Servicais (contract laborers from Angola, Mozambique, and Cabo Verde), Tongas (children of servicais born on the islands), Europeans (primarily Portuguese), Asians (mostly Chinese)</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>Catholic 55.7%, Adventist 4.1%, Assembly of God 3.4%, New Apostolic 2.9%, Mana 2.3%, Universal Kingdom of God 2%, Jehovah's Witness 1.2%, other 6.2%, none 21.2%, unspecified 1% (2012 est.)</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>Portuguese 98.4% (official), Forro 36.2%, Cabo Verdian 8.5%, French 6.8%, Angolar 6.6%, English 4.9%, Lunguie 1%, other (including sign language) 2.4%; other Portuguese-based Creoles are also spoken (2012 est.)</t>
         </is>
       </c>
-      <c r="M26" s="2" t="n">
+      <c r="O26" s="4" t="n">
         <v>0.8740000000000001</v>
       </c>
-      <c r="N26" s="2" t="n">
+      <c r="P26" s="4" t="n">
         <v>0.962</v>
       </c>
-      <c r="O26" s="2" t="n">
+      <c r="Q26" s="4" t="n">
         <v>0.895</v>
       </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>6 districts</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>$764.274 million (2024 est.)</t>
         </is>
       </c>
-      <c r="R26" s="2" t="n">
+      <c r="T26" s="4" t="n">
         <v>0.009000000000000001</v>
       </c>
-      <c r="S26" s="2" t="inlineStr">
+      <c r="U26" s="2" t="inlineStr">
         <is>
           <t>$5,500 (2024 est.)</t>
         </is>
       </c>
-      <c r="T26" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>9.2% (2024 est.)</t>
         </is>
       </c>
-      <c r="U26" s="2" t="inlineStr">
+      <c r="W26" s="2" t="inlineStr">
         <is>
           <t>66.7% (2017 est.)</t>
         </is>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="X26" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: NA
 highest 10%: NA</t>
         </is>
       </c>
-      <c r="W26" s="2" t="n">
+      <c r="Y26" s="4" t="n">
         <v>0.144</v>
       </c>
-      <c r="X26" s="2" t="n">
+      <c r="Z26" s="3" t="n">
         <v>165761</v>
       </c>
-      <c r="Y26" s="2" t="n">
+      <c r="AA26" s="4" t="n">
         <v>0.7747723745956961</v>
       </c>
-      <c r="Z26" s="2" t="n">
+      <c r="AB26" s="3" t="n">
         <v>61193</v>
       </c>
-      <c r="AA26" s="2" t="n">
+      <c r="AC26" s="4" t="n">
         <v>0.2860180978555537</v>
       </c>
-      <c r="AB26" s="2" t="n">
+      <c r="AD26" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AC26" s="2" t="n">
+      <c r="AE26" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AD26" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE26" s="2" t="n">
+      <c r="AF26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG26" s="3" t="n">
         <v>170801</v>
       </c>
-      <c r="AF26" s="2" t="n">
+      <c r="AH26" s="3" t="n">
         <v>81376</v>
       </c>
-      <c r="AG26" s="2" t="n">
+      <c r="AI26" s="3" t="n">
         <v>142703.316</v>
       </c>
     </row>
@@ -3770,121 +4038,131 @@
           <t>DRC</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
         <v>2267048</v>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="E27" s="3" t="n">
         <v>119038825</v>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="F27" s="4" t="n">
         <v>0.0309</v>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="G27" s="4" t="n">
         <v>0.457</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="H27" s="4" t="n">
         <v>0.518</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="I27" s="4" t="n">
         <v>0.025</v>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>16.9 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
+      <c r="K27" s="4" t="n">
         <v>0.474</v>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>more than 200 African ethnic groups of which the majority are Bantu; the four largest groups - Mongo, Luba, Kongo (all Bantu), and the Mangbetu-Azande (Hamitic) - make up about 45% of the population</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>&amp;nbsp;Christian 93/1% (Roman Catholic 29.9%, Protestant 26.7%, other Christian 36.5%), Kimbanguist 2.8%, Muslim 1.3%, other (includes syncretic sects and indigenous beliefs) 1.2%, none 1.3%, unspecified 0.2% (2014 est.)</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>French (official), Lingala (a lingua franca trade language), Kingwana (a dialect of Kiswahili or Swahili), Kikongo, Tshiluba</t>
         </is>
       </c>
-      <c r="M27" s="2" t="n">
+      <c r="O27" s="4" t="n">
         <v>0.736</v>
       </c>
-      <c r="N27" s="2" t="n">
+      <c r="P27" s="4" t="n">
         <v>0.885</v>
       </c>
-      <c r="O27" s="2" t="n">
+      <c r="Q27" s="4" t="n">
         <v>0.665</v>
       </c>
-      <c r="P27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>26 provinces</t>
         </is>
       </c>
-      <c r="Q27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
         <is>
           <t>$70.749 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R27" s="2" t="n">
+      <c r="T27" s="4" t="n">
         <v>0.067</v>
       </c>
-      <c r="S27" s="2" t="inlineStr">
+      <c r="U27" s="2" t="inlineStr">
         <is>
           <t>$1,500 (2024 est.)</t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>4.6% (2024 est.)</t>
         </is>
       </c>
-      <c r="U27" s="2" t="inlineStr">
+      <c r="W27" s="2" t="inlineStr">
         <is>
           <t>63% (2014 est.)</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="X27" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2.3%
 highest 10%: 34.7% (2006)</t>
         </is>
       </c>
-      <c r="W27" s="2" t="n">
+      <c r="Y27" s="4" t="n">
         <v>0.415</v>
       </c>
-      <c r="X27" s="2" t="n">
+      <c r="Z27" s="3" t="n">
         <v>42166976</v>
       </c>
-      <c r="Y27" s="2" t="n">
+      <c r="AA27" s="4" t="n">
         <v>0.4014195640204261</v>
       </c>
-      <c r="Z27" s="2" t="n">
+      <c r="AB27" s="3" t="n">
         <v>8231357</v>
       </c>
-      <c r="AA27" s="2" t="n">
+      <c r="AC27" s="4" t="n">
         <v>0.07836055728152008</v>
       </c>
-      <c r="AB27" s="2" t="n">
+      <c r="AD27" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="AC27" s="2" t="n">
+      <c r="AE27" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AD27" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE27" s="2" t="n">
+      <c r="AF27" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG27" s="3" t="n">
         <v>56424403</v>
       </c>
-      <c r="AF27" s="2" t="n">
+      <c r="AH27" s="3" t="n">
         <v>54400743</v>
       </c>
-      <c r="AG27" s="2" t="n">
+      <c r="AI27" s="3" t="n">
         <v>66178126.98</v>
       </c>
     </row>
@@ -3894,123 +4172,133 @@
           <t>Angola</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
         <v>1246700</v>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="E28" s="3" t="n">
         <v>38984796</v>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="F28" s="4" t="n">
         <v>0.0332</v>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="G28" s="4" t="n">
         <v>0.469</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="H28" s="4" t="n">
         <v>0.507</v>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="I28" s="4" t="n">
         <v>0.024</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>16.6 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="K28" s="4" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Ovimbundu 37%, Kimbundu 25%, Bakongo 13%, Mestico (mixed European and native African) 2%, European 1%, other 22%</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>Roman Catholic 41.1%, Protestant 38.1%, other 8.6%, none 12.3% (2014 est.)</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>Portuguese 71.2% (official), Umbundu 23%, Kikongo 8.2%, Kimbundu 7.8%, Chokwe 6.5%, Nhaneca 3.4%, Nganguela 3.1%, Fiote 2.4%, Kwanhama 2.3%, Muhumbi 2.1%, Luvale 1%, other 3.6%  (2014 est.)</t>
         </is>
       </c>
-      <c r="M28" s="2" t="n">
+      <c r="O28" s="4" t="n">
         <v>0.662</v>
       </c>
-      <c r="N28" s="2" t="n">
+      <c r="P28" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">60.7% </t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>18 provinces</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>$80.397 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R28" s="2" t="n">
+      <c r="T28" s="4" t="n">
         <v>0.044</v>
       </c>
-      <c r="S28" s="2" t="inlineStr">
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>$7,300 (2024 est.)</t>
         </is>
       </c>
-      <c r="T28" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>14.5% (2024 est.)</t>
         </is>
       </c>
-      <c r="U28" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>32.3% (2018 est.)</t>
         </is>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 0.6%
 highest 10%: 44.7% (2000)</t>
         </is>
       </c>
-      <c r="W28" s="2" t="n">
+      <c r="Y28" s="4" t="n">
         <v>0.282</v>
       </c>
-      <c r="X28" s="2" t="n">
+      <c r="Z28" s="3" t="n">
         <v>14830154</v>
       </c>
-      <c r="Y28" s="2" t="n">
+      <c r="AA28" s="4" t="n">
         <v>0.4408141381031682</v>
       </c>
-      <c r="Z28" s="2" t="n">
+      <c r="AB28" s="3" t="n">
         <v>4353033</v>
       </c>
-      <c r="AA28" s="2" t="n">
+      <c r="AC28" s="4" t="n">
         <v>0.1293903279783641</v>
       </c>
-      <c r="AB28" s="2" t="n">
+      <c r="AD28" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AC28" s="2" t="n">
+      <c r="AE28" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AD28" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE28" s="2" t="n">
+      <c r="AF28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG28" s="3" t="n">
         <v>26782555</v>
       </c>
-      <c r="AF28" s="2" t="n">
+      <c r="AH28" s="3" t="n">
         <v>18283869</v>
       </c>
-      <c r="AG28" s="2" t="n">
+      <c r="AI28" s="3" t="n">
         <v>10866574.658</v>
       </c>
     </row>
@@ -4020,117 +4308,127 @@
           <t>South Sudan</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
-        <v/>
-      </c>
-      <c r="C29" s="2" t="n">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E29" s="3" t="n">
         <v>12703714</v>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="F29" s="4" t="n">
         <v>0.0452</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="G29" s="4" t="n">
         <v>0.421</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="H29" s="4" t="n">
         <v>0.5529999999999999</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="I29" s="4" t="n">
         <v>0.026</v>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>18.7 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
+      <c r="K29" s="4" t="n">
         <v>0.212</v>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>Dinka (Jieng) approximately 35-40%, Nuer (Naath) approximately 15%, Shilluk (Chollo), Azande, Bari, Kakwa, Kuku, Murle, Mandari, Didinga, Ndogo, Bviri, Lndi, Anuak, Bongo, Lango, Dungotona, Acholi, Baka, Fertit (2011 est.)</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>Christian 60.5%, folk religion 32.9%, Muslim 6.2%, other &amp;lt;1%, unaffiliated &amp;lt;1% (2020 est.)</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>English (official), Arabic (includes Juba and Sudanese variants), regional languages include Dinka, Nuer, Bari, Zande, Shilluk</t>
         </is>
       </c>
-      <c r="M29" s="2" t="n">
+      <c r="O29" s="4" t="n">
         <v>0.345</v>
       </c>
-      <c r="N29" s="2" t="n">
+      <c r="P29" s="4" t="n">
         <v>0.403</v>
       </c>
-      <c r="O29" s="2" t="n">
+      <c r="Q29" s="4" t="n">
         <v>0.289</v>
       </c>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>10 states</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>$4.629 billion (2023 est.)</t>
         </is>
       </c>
-      <c r="R29" s="2" t="n">
+      <c r="T29" s="4" t="n">
         <v>-0.052</v>
       </c>
-      <c r="S29" s="2" t="n">
+      <c r="U29" s="2" t="n">
         <v>1600</v>
       </c>
-      <c r="T29" s="2" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
+      <c r="V29" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
         <is>
           <t>76.4% (2016 est.)</t>
         </is>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="X29" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: NA
 highest 10%: NA</t>
         </is>
       </c>
-      <c r="W29" s="2" t="n">
+      <c r="Y29" s="4" t="n">
         <v>0.914</v>
       </c>
-      <c r="X29" s="2" t="n">
+      <c r="Z29" s="3" t="n">
         <v>2221967</v>
       </c>
-      <c r="Y29" s="2" t="n">
+      <c r="AA29" s="4" t="n">
         <v>0.202289878964763</v>
       </c>
-      <c r="Z29" s="2" t="n">
+      <c r="AB29" s="3" t="n">
         <v>814326</v>
       </c>
-      <c r="AA29" s="2" t="n">
+      <c r="AC29" s="4" t="n">
         <v>0.07413697322141129</v>
       </c>
-      <c r="AB29" s="2" t="n">
+      <c r="AD29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AC29" s="2" t="n">
+      <c r="AE29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AD29" s="2" t="n">
+      <c r="AF29" s="2" t="n">
         <v>10984074</v>
       </c>
-      <c r="AE29" s="2" t="n">
+      <c r="AG29" s="3" t="n">
         <v>2693187</v>
       </c>
-      <c r="AF29" s="2" t="n">
+      <c r="AH29" s="3" t="n">
         <v>5348264</v>
       </c>
-      <c r="AG29" s="2" t="n">
+      <c r="AI29" s="3" t="n">
         <v>8391832.536</v>
       </c>
     </row>
@@ -4142,123 +4440,133 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1,096,570 </t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="E30" s="3" t="n">
         <v>121372632</v>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="F30" s="4" t="n">
         <v>0.0234</v>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="G30" s="4" t="n">
         <v>0.387</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="H30" s="4" t="n">
         <v>0.58</v>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="I30" s="4" t="n">
         <v>0.034</v>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>20.6 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="K30" s="4" t="n">
         <v>0.232</v>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>Oromo 35.8%, Amhara 24.1%, Somali 7.2%, Tigray 5.7%, Sidama 4.1%, Guragie 2.6%, Welaita 2.3%, Afar 2.2%, Silte 1.3%, Kefficho 1.2%, other 13.5% (2022 est.)</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>Ethiopian Orthodox 43.8%, Muslim 31.3%, Protestant 22.8%, Catholic 0.7%, traditional 0.6%, other 0.8% (2016 est.)</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>Oromo (official working language in the State of Oromiya) 33.8%, Amharic (official national language) 29.3%, Somali (official working language of the State of Sumale) 6.2%, Tigrigna (Tigrinya) (official working language of the State of Tigray) 5.9%, Sidamo 4%, Wolaytta 2.2%, Gurage 2%, Afar (official working language of the State of Afar) 1.7%, Hadiyya 1.7%, Gamo 1.5%, Gedeo 1.3%, Opuuo 1.2%, Kafa 1.1%, other 8.1%, English (major foreign language taught in schools), Arabic</t>
         </is>
       </c>
-      <c r="M30" s="2" t="n">
+      <c r="O30" s="4" t="n">
         <v>0.605</v>
       </c>
-      <c r="N30" s="2" t="n">
+      <c r="P30" s="4" t="n">
         <v>0.572</v>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">44.4% </t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>10 states</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>$126.773 billion (2022 est.)</t>
         </is>
       </c>
-      <c r="R30" s="2" t="n">
+      <c r="T30" s="4" t="n">
         <v>0.073</v>
       </c>
-      <c r="S30" s="2" t="inlineStr">
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>$2,900 (2024 est.)</t>
         </is>
       </c>
-      <c r="T30" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>3.4% (2024 est.)</t>
         </is>
       </c>
-      <c r="U30" s="2" t="inlineStr">
+      <c r="W30" s="2" t="inlineStr">
         <is>
           <t>23.5% (2015 est.)</t>
         </is>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="X30" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 4.1%
 highest 10%: 25.6% (2005)</t>
         </is>
       </c>
-      <c r="W30" s="2" t="n">
+      <c r="Y30" s="4" t="n">
         <v>0.21</v>
       </c>
-      <c r="X30" s="2" t="n">
+      <c r="Z30" s="3" t="n">
         <v>38147361</v>
       </c>
-      <c r="Y30" s="2" t="n">
+      <c r="AA30" s="4" t="n">
         <v>0.3440696875994596</v>
       </c>
-      <c r="Z30" s="2" t="n">
+      <c r="AB30" s="3" t="n">
         <v>19118470</v>
       </c>
-      <c r="AA30" s="2" t="n">
+      <c r="AC30" s="4" t="n">
         <v>0.1724388221843089</v>
       </c>
-      <c r="AB30" s="2" t="n">
+      <c r="AD30" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="AC30" s="2" t="n">
+      <c r="AE30" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AD30" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE30" s="2" t="n">
+      <c r="AF30" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG30" s="3" t="n">
         <v>28158451</v>
       </c>
-      <c r="AF30" s="2" t="n">
+      <c r="AH30" s="3" t="n">
         <v>46971209</v>
       </c>
-      <c r="AG30" s="2" t="n">
+      <c r="AI30" s="3" t="n">
         <v>26054692.285</v>
       </c>
     </row>
@@ -4268,123 +4576,133 @@
           <t>Eritrea</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
         <v>101000</v>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="E31" s="3" t="n">
         <v>6416435</v>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="F31" s="4" t="n">
         <v>0.0116</v>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="G31" s="4" t="n">
         <v>0.357</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="H31" s="4" t="n">
         <v>0.603</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="I31" s="4" t="n">
         <v>0.04</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>21.7 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
+      <c r="K31" s="4" t="n">
         <v>0.433</v>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>Tigrinya 50%, Tigre 30%, Saho 4%, Afar 4%, Kunama 4%, Bilen 3%, Hedareb/Beja 2%, Nara 2%, Rashaida 1% (2021 est.)</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>Eritrean Orthodox, Roman Catholic, Evangelical Lutheran, Sunni Muslim</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>Tigrinya (official), Arabic (official), English (official), Tigre, Kunama, Afar, other Cushitic languages</t>
         </is>
       </c>
-      <c r="M31" s="2" t="n">
+      <c r="O31" s="4" t="n">
         <v>0.766</v>
       </c>
-      <c r="N31" s="2" t="n">
+      <c r="P31" s="4" t="n">
         <v>0.844</v>
       </c>
-      <c r="O31" s="2" t="n">
+      <c r="Q31" s="4" t="n">
         <v>0.6889999999999999</v>
       </c>
-      <c r="P31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>6 regions</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr">
+      <c r="S31" s="2" t="inlineStr">
         <is>
           <t>$2.535 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R31" s="2" t="n">
+      <c r="T31" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="S31" s="2" t="inlineStr">
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t>$700 (2024 est.)</t>
         </is>
       </c>
-      <c r="T31" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>5.6% (2024 est.)</t>
         </is>
       </c>
-      <c r="U31" s="2" t="inlineStr">
+      <c r="W31" s="2" t="inlineStr">
         <is>
           <t>50% (2004 est.)</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="X31" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: NA
 highest 10%: NA</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="Y31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">9% </t>
         </is>
       </c>
-      <c r="X31" s="2" t="n">
+      <c r="Z31" s="3" t="n">
         <v>1226660</v>
       </c>
-      <c r="Y31" s="2" t="n">
+      <c r="AA31" s="4" t="n">
         <v>0.191174694359095</v>
       </c>
-      <c r="Z31" s="2" t="n">
+      <c r="AB31" s="3" t="n">
         <v>78215</v>
       </c>
-      <c r="AA31" s="2" t="n">
+      <c r="AC31" s="4" t="n">
         <v>0.01218979074828935</v>
       </c>
-      <c r="AB31" s="2" t="n">
+      <c r="AD31" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AC31" s="2" t="n">
+      <c r="AE31" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AD31" s="2" t="n">
+      <c r="AF31" s="2" t="n">
         <v>6147398</v>
       </c>
-      <c r="AE31" s="2" t="n">
+      <c r="AG31" s="3" t="n">
         <v>2778316</v>
       </c>
-      <c r="AF31" s="2" t="n">
+      <c r="AH31" s="3" t="n">
         <v>2290667</v>
       </c>
-      <c r="AG31" s="2" t="n">
+      <c r="AI31" s="3" t="n">
         <v>3208217.5</v>
       </c>
     </row>
@@ -4394,121 +4712,131 @@
           <t>Djibouti</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
         <v>23180</v>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="E32" s="3" t="n">
         <v>1013703</v>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="F32" s="4" t="n">
         <v>0.0184</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="G32" s="4" t="n">
         <v>0.284</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="H32" s="4" t="n">
         <v>0.674</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="I32" s="4" t="n">
         <v>0.042</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>26.7 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
+      <c r="K32" s="4" t="n">
         <v>0.7859999999999999</v>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>Somali 60%, Afar 35%, other 5% (mostly Yemeni Arab, also French, Ethiopian, and Italian)</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>Sunni Muslim 94% (nearly all Djiboutians), other 6% (mainly foreign-born residents - Shia Muslim, Christian, Hindu, Jewish, Baha'i, and atheist)</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>French (official), Arabic (official), Somali, Afar</t>
         </is>
       </c>
-      <c r="M32" s="2" t="n">
-        <v/>
-      </c>
-      <c r="N32" s="2" t="n">
-        <v/>
-      </c>
-      <c r="O32" s="2" t="n">
-        <v/>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="O32" s="4" t="n">
+        <v/>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>6 districts</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>$4.086 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R32" s="2" t="n">
+      <c r="T32" s="4" t="n">
         <v>0.06</v>
       </c>
-      <c r="S32" s="2" t="inlineStr">
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>$6,800 (2024 est.)</t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>25.9% (2024 est.)</t>
         </is>
       </c>
-      <c r="U32" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>21.1% (2017 est.)</t>
         </is>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2.4%
 highest 10%: 30.9% (2002)</t>
         </is>
       </c>
-      <c r="W32" s="2" t="n">
+      <c r="Y32" s="4" t="n">
         <v>0.021</v>
       </c>
-      <c r="X32" s="2" t="n">
+      <c r="Z32" s="3" t="n">
         <v>413866</v>
       </c>
-      <c r="Y32" s="2" t="n">
+      <c r="AA32" s="4" t="n">
         <v>0.4082714562352089</v>
       </c>
-      <c r="Z32" s="2" t="n">
+      <c r="AB32" s="3" t="n">
         <v>492221</v>
       </c>
-      <c r="AA32" s="2" t="n">
+      <c r="AC32" s="4" t="n">
         <v>0.4855672716762208</v>
       </c>
-      <c r="AB32" s="2" t="n">
+      <c r="AD32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AC32" s="2" t="n">
+      <c r="AE32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AD32" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE32" s="2" t="n">
+      <c r="AF32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG32" s="3" t="n">
         <v>796771</v>
       </c>
-      <c r="AF32" s="2" t="n">
+      <c r="AH32" s="3" t="n">
         <v>287892</v>
       </c>
-      <c r="AG32" s="2" t="n">
+      <c r="AI32" s="3" t="n">
         <v>213891.333</v>
       </c>
     </row>
@@ -4518,119 +4846,129 @@
           <t>Somalia</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
         <v>627337</v>
       </c>
-      <c r="C33" s="2" t="n">
+      <c r="E33" s="3" t="n">
         <v>20324160</v>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="F33" s="4" t="n">
         <v>0.0332</v>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="G33" s="4" t="n">
         <v>0.414</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="H33" s="4" t="n">
         <v>0.5579999999999999</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="I33" s="4" t="n">
         <v>0.028</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>15.7 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
+      <c r="K33" s="4" t="n">
         <v>0.479</v>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>predominantly Somali with lesser numbers of Arabs, Bantus, and others</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Muslim 99.9% (Sunni Muslim 98.1%, Shia Muslim 1.2%, Islamic schismatic 0.6%), ethnic religionist 0.1% (2020 est.)</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>Somali (official, according to the 2012 Transitional Federal Charter), Arabic (official, according to the 2012 Transitional Federal Charter), Italian, English</t>
         </is>
       </c>
-      <c r="M33" s="2" t="n">
+      <c r="O33" s="4" t="n">
         <v>0.541</v>
       </c>
-      <c r="N33" s="2" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="2" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
+      <c r="P33" s="4" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="4" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
         <is>
           <t>18 regions</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr">
+      <c r="S33" s="2" t="inlineStr">
         <is>
           <t>$12.109 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R33" s="2" t="n">
+      <c r="T33" s="4" t="n">
         <v>0.04</v>
       </c>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="U33" s="2" t="inlineStr">
         <is>
           <t>$1,400 (2024 est.)</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>18.9% (2024 est.)</t>
         </is>
       </c>
-      <c r="U33" s="2" t="n">
+      <c r="W33" s="2" t="n">
         <v>0.544</v>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="X33" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: NA
 highest 10%: NA</t>
         </is>
       </c>
-      <c r="W33" s="2" t="n">
+      <c r="Y33" s="4" t="n">
         <v>0.015</v>
       </c>
-      <c r="X33" s="2" t="n">
+      <c r="Z33" s="3" t="n">
         <v>5612338</v>
       </c>
-      <c r="Y33" s="2" t="n">
+      <c r="AA33" s="4" t="n">
         <v>0.2761412033756869</v>
       </c>
-      <c r="Z33" s="2" t="n">
+      <c r="AB33" s="3" t="n">
         <v>225181</v>
       </c>
-      <c r="AA33" s="2" t="n">
+      <c r="AC33" s="4" t="n">
         <v>0.01107947388723568</v>
       </c>
-      <c r="AB33" s="2" t="n">
+      <c r="AD33" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="AC33" s="2" t="n">
+      <c r="AE33" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AD33" s="2" t="n">
+      <c r="AF33" s="2" t="n">
         <v>12094640</v>
       </c>
-      <c r="AE33" s="2" t="n">
+      <c r="AG33" s="3" t="n">
         <v>9735273</v>
       </c>
-      <c r="AF33" s="2" t="n">
+      <c r="AH33" s="3" t="n">
         <v>8414202</v>
       </c>
-      <c r="AG33" s="2" t="n">
+      <c r="AI33" s="3" t="n">
         <v>11076667.2</v>
       </c>
     </row>
@@ -4640,123 +4978,133 @@
           <t>Kenya</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
         <v>569140</v>
       </c>
-      <c r="C34" s="2" t="n">
+      <c r="E34" s="3" t="n">
         <v>55751717</v>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="F34" s="4" t="n">
         <v>0.0215</v>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="G34" s="4" t="n">
         <v>0.358</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="H34" s="4" t="n">
         <v>0.609</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="I34" s="4" t="n">
         <v>0.034</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>21.5 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
+      <c r="K34" s="4" t="n">
         <v>0.295</v>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>Kikuyu 17.1%, Luhya 14.3%, Kalenjin 13.4%, Luo 10.7%, Kamba 9.8%, Somali 5.8%, Kisii 5.7%, Mijikenda 5.2%, Meru 4.2%, Maasai 2.5%, Turkana 2.1%,&amp;nbsp;non-Kenyan 1%, other 8.2% (2019 est.)</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>Christian 85.5% (Protestant 33.4%, Catholic 20.6%, Evangelical 20.4%, African Instituted Churches 7%, other Christian 4.1%), Muslim 10.9%, other 1.8%, none 1.6%,&amp;nbsp;don't&amp;nbsp;know/no answer&amp;nbsp;0.2% (2019 est.)</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>English (official), Kiswahili (official), numerous indigenous languages</t>
         </is>
       </c>
-      <c r="M34" s="2" t="n">
+      <c r="O34" s="4" t="n">
         <v>0.8149999999999999</v>
       </c>
-      <c r="N34" s="2" t="n">
+      <c r="P34" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="O34" s="2" t="n">
+      <c r="Q34" s="4" t="n">
         <v>0.782</v>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>47 counties</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>$124.499 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R34" s="2" t="n">
+      <c r="T34" s="4" t="n">
         <v>0.045</v>
       </c>
-      <c r="S34" s="2" t="inlineStr">
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>$5,800 (2024 est.)</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>5.5% (2024 est.)</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t>38,6% (2021 est.)</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="X34" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 1.8%
 highest 10%: 37.8% (2005)</t>
         </is>
       </c>
-      <c r="W34" s="2" t="n">
+      <c r="Y34" s="4" t="n">
         <v>0.045</v>
       </c>
-      <c r="X34" s="2" t="n">
+      <c r="Z34" s="3" t="n">
         <v>54555497</v>
       </c>
-      <c r="Y34" s="2" t="n">
+      <c r="AA34" s="4" t="n">
         <v>0.9785437998259319</v>
       </c>
-      <c r="Z34" s="2" t="n">
+      <c r="AB34" s="3" t="n">
         <v>9129243</v>
       </c>
-      <c r="AA34" s="2" t="n">
+      <c r="AC34" s="4" t="n">
         <v>0.163748194517489</v>
       </c>
-      <c r="AB34" s="2" t="n">
+      <c r="AD34" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="AC34" s="2" t="n">
+      <c r="AE34" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AD34" s="2" t="inlineStr">
+      <c r="AF34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">54,685,051 </t>
         </is>
       </c>
-      <c r="AE34" s="2" t="n">
+      <c r="AG34" s="3" t="n">
         <v>16446757</v>
       </c>
-      <c r="AF34" s="2" t="n">
+      <c r="AH34" s="3" t="n">
         <v>19959115</v>
       </c>
-      <c r="AG34" s="2" t="n">
+      <c r="AI34" s="3" t="n">
         <v>21520162.762</v>
       </c>
     </row>
@@ -4768,123 +5116,133 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">197,100 </t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
+      <c r="E35" s="3" t="n">
         <v>50863850</v>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="F35" s="4" t="n">
         <v>0.0313</v>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="G35" s="4" t="n">
         <v>0.47</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="H35" s="4" t="n">
         <v>0.506</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="I35" s="4" t="n">
         <v>0.024</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>16.4 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
+      <c r="K35" s="4" t="n">
         <v>0.268</v>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>Baganda 16.5%, Banyankole 9.6%, Basoga 8.8%, Bakiga 7.1%, Iteso 7%, Langi 6.3%, Bagisu 4.9%, Acholi 4.4%, Lugbara 3.3%, other 32.1% (2014 est.)</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>Protestant 45.1% (Anglican 32.0%, Pentecostal/Born Again/Evangelical 11.1%, Seventh Day Adventist 1.7%, Baptist .3%), Roman Catholic 39.3%, Muslim 13.7%, other 1.6%, none 0.2% (2014 est.)</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>English (official), Ganda or Luganda (most widely used of the Niger-Congo languages and the language used most often in the capital), other Niger-Congo languages, Nilo-Saharan languages, Swahili (official), Arabic</t>
         </is>
       </c>
-      <c r="M35" s="2" t="n">
+      <c r="O35" s="4" t="n">
         <v>0.6909999999999999</v>
       </c>
-      <c r="N35" s="2" t="n">
+      <c r="P35" s="4" t="n">
         <v>0.827</v>
       </c>
-      <c r="O35" s="2" t="n">
+      <c r="Q35" s="4" t="n">
         <v>0.708</v>
       </c>
-      <c r="P35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>134 districts</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
         <is>
           <t>$53.652 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R35" s="2" t="n">
+      <c r="T35" s="4" t="n">
         <v>0.061</v>
       </c>
-      <c r="S35" s="2" t="inlineStr">
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>$2,900 (2024 est.)</t>
         </is>
       </c>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>3% (2024 est.)</t>
         </is>
       </c>
-      <c r="U35" s="2" t="inlineStr">
+      <c r="W35" s="2" t="inlineStr">
         <is>
           <t>20.3% (2019 est.)</t>
         </is>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="X35" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2.4%
 highest 10%: 36.1% (2009 est.)</t>
         </is>
       </c>
-      <c r="W35" s="2" t="n">
+      <c r="Y35" s="4" t="n">
         <v>0.033</v>
       </c>
-      <c r="X35" s="2" t="n">
+      <c r="Z35" s="3" t="n">
         <v>25395503</v>
       </c>
-      <c r="Y35" s="2" t="n">
+      <c r="AA35" s="4" t="n">
         <v>0.4992839315152117</v>
       </c>
-      <c r="Z35" s="2" t="inlineStr">
+      <c r="AB35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 9,620,681</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AB35" s="2" t="n">
+      <c r="AC35" s="4" t="n">
+        <v/>
+      </c>
+      <c r="AD35" s="2" t="n">
         <v>258</v>
       </c>
-      <c r="AC35" s="2" t="n">
+      <c r="AE35" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="AD35" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE35" s="2" t="n">
+      <c r="AF35" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG35" s="3" t="n">
         <v>13631512</v>
       </c>
-      <c r="AF35" s="2" t="n">
+      <c r="AH35" s="3" t="n">
         <v>23906010</v>
       </c>
-      <c r="AG35" s="2" t="n">
+      <c r="AI35" s="3" t="n">
         <v>10325361.55</v>
       </c>
     </row>
@@ -4894,121 +5252,131 @@
           <t>Tanzania</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
         <v>885800</v>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="E36" s="3" t="n">
         <v>69145464</v>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="F36" s="4" t="n">
         <v>0.0285</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="G36" s="4" t="n">
         <v>0.412</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="H36" s="4" t="n">
         <v>0.5539999999999999</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="I36" s="4" t="n">
         <v>0.034</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>18.8 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="K36" s="4" t="n">
         <v>0.374</v>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>mainland - African 99% (of which 95% are Bantu consisting of more than 130 tribes), other 1% (consisting of Asian, European, and Arab); Zanzibar - Arab, African, mixed Arab and African</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>Christian 63.1%, Muslim 34.1%, folk religion 1.1%, Buddhist &amp;lt;1%, Hindu &amp;lt;1%, Jewish &amp;lt;1%, other &amp;lt;1%, unspecified 1.6% (2020 est.)</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>Kiswahili or Swahili (official), Kiunguja (name for Swahili in Zanzibar), English (official, primary language of commerce, administration, and higher education), Arabic (widely spoken in Zanzibar), many local languages</t>
         </is>
       </c>
-      <c r="M36" s="2" t="n">
+      <c r="O36" s="4" t="n">
         <v>0.782</v>
       </c>
-      <c r="N36" s="2" t="n">
+      <c r="P36" s="4" t="n">
         <v>0.832</v>
       </c>
-      <c r="O36" s="2" t="n">
+      <c r="Q36" s="4" t="n">
         <v>0.731</v>
       </c>
-      <c r="P36" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>31 regions</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>$78.78 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R36" s="2" t="n">
+      <c r="T36" s="4" t="n">
         <v>0.055</v>
       </c>
-      <c r="S36" s="2" t="inlineStr">
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>$3,700 (2024 est.)</t>
         </is>
       </c>
-      <c r="T36" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>2.6% (2024 est.)</t>
         </is>
       </c>
-      <c r="U36" s="2" t="inlineStr">
+      <c r="W36" s="2" t="inlineStr">
         <is>
           <t>26.4% (2018 est.)</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="X36" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2.8%
 highest 10%: 29.6% (2007)</t>
         </is>
       </c>
-      <c r="W36" s="2" t="n">
+      <c r="Y36" s="4" t="n">
         <v>0.031</v>
       </c>
-      <c r="X36" s="2" t="n">
+      <c r="Z36" s="3" t="n">
         <v>47685232</v>
       </c>
-      <c r="Y36" s="2" t="n">
+      <c r="AA36" s="4" t="n">
         <v>0.6896364452771624</v>
       </c>
-      <c r="Z36" s="2" t="n">
+      <c r="AB36" s="3" t="n">
         <v>13862836</v>
       </c>
-      <c r="AA36" s="2" t="n">
+      <c r="AC36" s="4" t="n">
         <v>0.2004880030886769</v>
       </c>
-      <c r="AB36" s="2" t="n">
+      <c r="AD36" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="AC36" s="2" t="n">
+      <c r="AE36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AD36" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE36" s="2" t="n">
+      <c r="AF36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG36" s="3" t="n">
         <v>25860404</v>
       </c>
-      <c r="AF36" s="2" t="n">
+      <c r="AH36" s="3" t="n">
         <v>28487931</v>
       </c>
-      <c r="AG36" s="2" t="n">
+      <c r="AI36" s="3" t="n">
         <v>18254402.496</v>
       </c>
     </row>
@@ -5018,121 +5386,131 @@
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
         <v>24668</v>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="E37" s="3" t="n">
         <v>13623302</v>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="F37" s="4" t="n">
         <v>0.02</v>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="G37" s="4" t="n">
         <v>0.3720000000000001</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="H37" s="4" t="n">
         <v>0.597</v>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="I37" s="4" t="n">
         <v>0.031</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>21.3 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
+      <c r="K37" s="4" t="n">
         <v>0.179</v>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>Hutu, Tutsi, Twa</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>Catholic 39.9%, Pentecostal 21.3%, Protestant 14.6%, Adventist 12.2%, other Christians 4.2%, no religion 3.0%, Muslim 2.0%, other religions 2.0%; less than 1%: Jehovah Witness, not specified, Animist&amp;nbsp; (2022 est.)</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>Kinyarwanda (official, universal Bantu vernacular) 93.2%, French (official) &lt;.1, English (official) &lt;.1, Swahili/Kiswahili (official, used in commercial centers) &lt;.1, more than one language, other 6.3%, unspecified 0.3%</t>
         </is>
       </c>
-      <c r="M37" s="2" t="n">
+      <c r="O37" s="4" t="n">
         <v>0.7879999999999999</v>
       </c>
-      <c r="N37" s="2" t="n">
+      <c r="P37" s="4" t="n">
         <v>0.776</v>
       </c>
-      <c r="O37" s="2" t="n">
+      <c r="Q37" s="4" t="n">
         <v>0.694</v>
       </c>
-      <c r="P37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>4 provinces</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>$14.252 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R37" s="2" t="n">
+      <c r="T37" s="4" t="n">
         <v>0.08900000000000001</v>
       </c>
-      <c r="S37" s="2" t="inlineStr">
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>$3,300 (2024 est.)</t>
         </is>
       </c>
-      <c r="T37" s="2" t="inlineStr">
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>12% (2024 est.)</t>
         </is>
       </c>
-      <c r="U37" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>38.2% (2016 est.)</t>
         </is>
       </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2.1%
 highest 10%: 43.2% (2011 est.)</t>
         </is>
       </c>
-      <c r="W37" s="2" t="n">
+      <c r="Y37" s="4" t="n">
         <v>0.018</v>
       </c>
-      <c r="X37" s="2" t="n">
+      <c r="Z37" s="3" t="n">
         <v>9658548</v>
       </c>
-      <c r="Y37" s="2" t="n">
+      <c r="AA37" s="4" t="n">
         <v>0.7089726117794349</v>
       </c>
-      <c r="Z37" s="2" t="n">
+      <c r="AB37" s="3" t="n">
         <v>2653197</v>
       </c>
-      <c r="AA37" s="2" t="n">
+      <c r="AC37" s="4" t="n">
         <v>0.1947543260804172</v>
       </c>
-      <c r="AB37" s="2" t="n">
+      <c r="AD37" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="AC37" s="2" t="n">
+      <c r="AE37" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="AD37" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE37" s="2" t="n">
+      <c r="AF37" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG37" s="3" t="n">
         <v>2438571</v>
       </c>
-      <c r="AF37" s="2" t="n">
+      <c r="AH37" s="3" t="n">
         <v>5067868</v>
       </c>
-      <c r="AG37" s="2" t="n">
+      <c r="AI37" s="3" t="n">
         <v>5204101.364</v>
       </c>
     </row>
@@ -5142,121 +5520,131 @@
           <t>Burundi</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
         <v>25680</v>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="E38" s="3" t="n">
         <v>13590102</v>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="F38" s="4" t="n">
         <v>0.0296</v>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="G38" s="4" t="n">
         <v>0.423</v>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="H38" s="4" t="n">
         <v>0.544</v>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="I38" s="4" t="n">
         <v>0.034</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>17.6 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
+      <c r="K38" s="4" t="n">
         <v>0.148</v>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>Hutu, Tutsi, Twa, South Asian</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>Christian 93.9% (Roman Catholic 58.6%, Protestant 35.3% [includes Adventist 2.7% and other Protestant religions 32.6%]), Muslim 3.4%, other 1.3%, none 1.3% (2016-17 est.)</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>Kirundi only 29.7% (official); French only .3% (official); Swahili only .2%; English only .1% (official); Kirundi and French 8.4%; Kirundi, French, and English 2.4%, other language combinations 2%, unspecified 56.9%</t>
         </is>
       </c>
-      <c r="M38" s="2" t="n">
+      <c r="O38" s="4" t="n">
         <v>0.7140000000000001</v>
       </c>
-      <c r="N38" s="2" t="n">
+      <c r="P38" s="4" t="n">
         <v>0.763</v>
       </c>
-      <c r="O38" s="2" t="n">
+      <c r="Q38" s="4" t="n">
         <v>0.612</v>
       </c>
-      <c r="P38" s="2" t="inlineStr">
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t>18 provinces</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr">
+      <c r="S38" s="2" t="inlineStr">
         <is>
           <t>$2.162 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R38" s="2" t="n">
+      <c r="T38" s="4" t="n">
         <v>0.035</v>
       </c>
-      <c r="S38" s="2" t="inlineStr">
+      <c r="U38" s="2" t="inlineStr">
         <is>
           <t>$800 (2024 est.)</t>
         </is>
       </c>
-      <c r="T38" s="2" t="inlineStr">
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>1% (2024 est.)</t>
         </is>
       </c>
-      <c r="U38" s="2" t="inlineStr">
+      <c r="W38" s="2" t="inlineStr">
         <is>
           <t>51% (2020 est.)</t>
         </is>
       </c>
-      <c r="V38" s="2" t="inlineStr">
+      <c r="X38" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 4.1%
 highest 10%: 28% (2006)</t>
         </is>
       </c>
-      <c r="W38" s="2" t="n">
+      <c r="Y38" s="4" t="n">
         <v>0.202</v>
       </c>
-      <c r="X38" s="2" t="n">
+      <c r="Z38" s="3" t="n">
         <v>6532039</v>
       </c>
-      <c r="Y38" s="2" t="n">
+      <c r="AA38" s="4" t="n">
         <v>0.4806467972057899</v>
       </c>
-      <c r="Z38" s="2" t="n">
+      <c r="AB38" s="3" t="n">
         <v>298684</v>
       </c>
-      <c r="AA38" s="2" t="n">
+      <c r="AC38" s="4" t="n">
         <v>0.02197805432218242</v>
       </c>
-      <c r="AB38" s="2" t="n">
+      <c r="AD38" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="AC38" s="2" t="n">
+      <c r="AE38" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AD38" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE38" s="2" t="n">
+      <c r="AF38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG38" s="3" t="n">
         <v>2011335</v>
       </c>
-      <c r="AF38" s="2" t="n">
+      <c r="AH38" s="3" t="n">
         <v>5748613</v>
       </c>
-      <c r="AG38" s="2" t="n">
+      <c r="AI38" s="3" t="n">
         <v>6930952.02</v>
       </c>
     </row>
@@ -5268,121 +5656,131 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">94,080 </t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
+      <c r="E39" s="3" t="n">
         <v>21763309</v>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="F39" s="4" t="n">
         <v>0.0216</v>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="G39" s="4" t="n">
         <v>0.377</v>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="H39" s="4" t="n">
         <v>0.584</v>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="I39" s="4" t="n">
         <v>0.039</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>19.4 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
+      <c r="K39" s="4" t="n">
         <v>0.183</v>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>Chewa 34.3%, Lomwe 18.8%, Yao 13.2%, Ngoni 10.4%, Tumbuka 9.2%, Sena 3.8%, Mang'anja 3.2%, Tonga 1.8%, Nyanja 1.8%, Nkhonde 1%, other 2.2%, foreign 0.3% (2018 est.)</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>Protestant 33.5% (includes Church of Central Africa Presbyterian 14.2%, Seventh Day Adventist/Baptist 9.4%, Pentecostal 7.6%, Anglican 2.3%), Roman Catholic 17.2%, other Christian 26.6%, Muslim 13.8%, traditionalist 1.1%, other 5.6%, none 2.1% (2018 est.)</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>English (official), Chewa (dominant), Lambya, Lomwe, Ngoni, Nkhonde, Nyakyusa, Nyanja, Sena, Tonga, Tumbuka, Yao</t>
         </is>
       </c>
-      <c r="M39" s="2" t="n">
+      <c r="O39" s="4" t="n">
         <v>0.7020000000000001</v>
       </c>
-      <c r="N39" s="2" t="n">
+      <c r="P39" s="4" t="n">
         <v>0.698</v>
       </c>
-      <c r="O39" s="2" t="n">
+      <c r="Q39" s="4" t="n">
         <v>0.552</v>
       </c>
-      <c r="P39" s="2" t="inlineStr">
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>28 districts</t>
         </is>
       </c>
-      <c r="Q39" s="2" t="inlineStr">
+      <c r="S39" s="2" t="inlineStr">
         <is>
           <t>$11.009 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R39" s="2" t="n">
+      <c r="T39" s="4" t="n">
         <v>0.018</v>
       </c>
-      <c r="S39" s="2" t="inlineStr">
+      <c r="U39" s="2" t="inlineStr">
         <is>
           <t>$1,600 (2024 est.)</t>
         </is>
       </c>
-      <c r="T39" s="2" t="inlineStr">
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>5.1% (2024 est.)</t>
         </is>
       </c>
-      <c r="U39" s="2" t="inlineStr">
+      <c r="W39" s="2" t="inlineStr">
         <is>
           <t>1.8% (2024 est.)</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="X39" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2.2%
 highest 10%: 37.5% (2010 est.)</t>
         </is>
       </c>
-      <c r="W39" s="2" t="n">
+      <c r="Y39" s="4" t="n">
         <v>0.322</v>
       </c>
-      <c r="X39" s="2" t="n">
+      <c r="Z39" s="3" t="n">
         <v>8901027</v>
       </c>
-      <c r="Y39" s="2" t="n">
+      <c r="AA39" s="4" t="n">
         <v>0.4089923549769017</v>
       </c>
-      <c r="Z39" s="2" t="n">
+      <c r="AB39" s="3" t="n">
         <v>2734305</v>
       </c>
-      <c r="AA39" s="2" t="n">
+      <c r="AC39" s="4" t="n">
         <v>0.1256382933312209</v>
       </c>
-      <c r="AB39" s="2" t="n">
+      <c r="AD39" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AC39" s="2" t="n">
+      <c r="AE39" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AD39" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE39" s="2" t="n">
+      <c r="AF39" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG39" s="3" t="n">
         <v>3982686</v>
       </c>
-      <c r="AF39" s="2" t="n">
+      <c r="AH39" s="3" t="n">
         <v>8204767</v>
       </c>
-      <c r="AG39" s="2" t="n">
+      <c r="AI39" s="3" t="n">
         <v>391739.562</v>
       </c>
     </row>
@@ -5392,123 +5790,133 @@
           <t>Zambia</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
         <v>743398</v>
       </c>
-      <c r="C40" s="2" t="n">
+      <c r="E40" s="3" t="n">
         <v>22021971</v>
       </c>
-      <c r="D40" s="2" t="n">
+      <c r="F40" s="4" t="n">
         <v>0.0251</v>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="G40" s="4" t="n">
         <v>0.421</v>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="H40" s="4" t="n">
         <v>0.551</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="I40" s="4" t="n">
         <v>0.028</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>19 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
+      <c r="K40" s="4" t="n">
         <v>0.463</v>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>Bemba 21%, Tonga 13.6%, Chewa 7.4%, Lozi 5.7%, Nsenga 5.3%, Tumbuka 4.4%, Ngoni 4%, Lala 3.1%, Kaonde 2.9%, Namwanga 2.8%, Lunda (north Western) 2.6%, Mambwe 2.5%, Luvale 2.2%, Lamba 2.1%, Ushi 1.9%, Lenje 1.6%, Bisa 1.6%, Mbunda 1.2%, other 13.8%, unspecified 0.4% (2010 est.)</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>Protestant 75.3%, Roman Catholic 20.2%, other 2.7% (includes Muslim, Buddhist, Hindu, and Baha'i), none 1.8% (2010 est.)</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>Bemba 33.4%, Nyanja 14.7%, Tonga 11.4%, Lozi 5.5%, Chewa 4.5%, Nsenga 2.9%, Tumbuka 2.5%, Lunda (North Western) 1.9%, Kaonde 1.8%, Lala 1.8%, Lamba 1.8%, English (official) 1.7%, Luvale 1.5%, Mambwe 1.3%, Namwanga 1.2%, Lenje 1.1%, Bisa 1%, other 9.7%, unspecified 0.2% (2010 est.)</t>
         </is>
       </c>
-      <c r="M40" s="2" t="n">
+      <c r="O40" s="4" t="n">
         <v>0.711</v>
       </c>
-      <c r="N40" s="2" t="n">
+      <c r="P40" s="4" t="n">
         <v>0.906</v>
       </c>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">83.1% </t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
+      <c r="R40" s="2" t="inlineStr">
         <is>
           <t>10 provinces</t>
         </is>
       </c>
-      <c r="Q40" s="2" t="inlineStr">
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t>$26.326 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R40" s="2" t="n">
+      <c r="T40" s="4" t="n">
         <v>0.04</v>
       </c>
-      <c r="S40" s="2" t="inlineStr">
+      <c r="U40" s="2" t="inlineStr">
         <is>
           <t>$3,700 (2024 est.)</t>
         </is>
       </c>
-      <c r="T40" s="2" t="inlineStr">
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>6% (2024 est.)</t>
         </is>
       </c>
-      <c r="U40" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>60% (2022 est.)</t>
         </is>
       </c>
-      <c r="V40" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 1.5%
 highest 10%: 47.4% (2010)</t>
         </is>
       </c>
-      <c r="W40" s="2" t="n">
+      <c r="Y40" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="X40" s="2" t="n">
+      <c r="Z40" s="3" t="n">
         <v>17220607</v>
       </c>
-      <c r="Y40" s="2" t="n">
-        <v/>
-      </c>
-      <c r="Z40" s="2" t="n">
+      <c r="AA40" s="4" t="n">
+        <v/>
+      </c>
+      <c r="AB40" s="3" t="n">
         <v>2351646</v>
       </c>
-      <c r="AA40" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AB40" s="2" t="n">
+      <c r="AC40" s="4" t="n">
+        <v/>
+      </c>
+      <c r="AD40" s="2" t="n">
         <v>137</v>
       </c>
-      <c r="AC40" s="2" t="n">
+      <c r="AE40" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="AD40" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE40" s="2" t="n">
+      <c r="AF40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG40" s="3" t="n">
         <v>10196173</v>
       </c>
-      <c r="AF40" s="2" t="n">
+      <c r="AH40" s="3" t="n">
         <v>9271250</v>
       </c>
-      <c r="AG40" s="2" t="n">
+      <c r="AI40" s="3" t="n">
         <v>13213182.6</v>
       </c>
     </row>
@@ -5518,121 +5926,131 @@
           <t>Zimbabwe</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
         <v>386847</v>
       </c>
-      <c r="C41" s="2" t="n">
+      <c r="E41" s="3" t="n">
         <v>17472752</v>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="F41" s="4" t="n">
         <v>0.0182</v>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="G41" s="4" t="n">
         <v>0.383</v>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="H41" s="4" t="n">
         <v>0.578</v>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="I41" s="4" t="n">
         <v>0.039</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>21.3 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
+      <c r="K41" s="4" t="n">
         <v>0.325</v>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>African 99.6% (predominantly Shona; Ndebele is the second largest ethnic group), other (includes Caucasian, Asiatic, mixed race) 0.4% (2022 est.)</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>Apostolic Sect 40.3%, Pentecostal 17%, Protestant 13.8%, other Christian 7.8%, Roman Catholic 6.4%, African traditionalist 5%, other 1.5% (includes Muslim, Jewish, Hindu), none 8.3% (2022 est.)</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>Shona (official, most widely spoken) 80.9%, Ndebele (official, second most widely spoken) 11.5%, English (official, traditionally used for official business) 0.3%, 13 minority languages (official; includes Chewa, Chibarwe, Kalanga, Koisan, Nambya, Ndau, Shangani, sign language, Sotho, Tonga, Tswana, Venda, and Xhosa) 7%, other 0.3% (2022 est.)</t>
         </is>
       </c>
-      <c r="M41" s="2" t="n">
+      <c r="O41" s="4" t="n">
         <v>0.9320000000000001</v>
       </c>
-      <c r="N41" s="2" t="n">
+      <c r="P41" s="4" t="n">
         <v>0.885</v>
       </c>
-      <c r="O41" s="2" t="n">
+      <c r="Q41" s="4" t="n">
         <v>0.846</v>
       </c>
-      <c r="P41" s="2" t="inlineStr">
+      <c r="R41" s="2" t="inlineStr">
         <is>
           <t>8 provinces</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr">
+      <c r="S41" s="2" t="inlineStr">
         <is>
           <t>$44.188 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R41" s="2" t="n">
+      <c r="T41" s="4" t="n">
         <v>0.02</v>
       </c>
-      <c r="S41" s="2" t="inlineStr">
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t>$3,500 (2024 est.)</t>
         </is>
       </c>
-      <c r="T41" s="2" t="inlineStr">
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>8.6% (2024 est.)</t>
         </is>
       </c>
-      <c r="U41" s="2" t="inlineStr">
+      <c r="W41" s="2" t="inlineStr">
         <is>
           <t>38.3% (2019 est.)</t>
         </is>
       </c>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="X41" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 2%
 highest 10%: 40.4% (1995)</t>
         </is>
       </c>
-      <c r="W41" s="2" t="n">
+      <c r="Y41" s="4" t="n">
         <v>2.417</v>
       </c>
-      <c r="X41" s="2" t="n">
+      <c r="Z41" s="3" t="n">
         <v>13195902</v>
       </c>
-      <c r="Y41" s="2" t="n">
+      <c r="AA41" s="4" t="n">
         <v>0.7552274535802946</v>
       </c>
-      <c r="Z41" s="2" t="n">
+      <c r="AB41" s="3" t="n">
         <v>3796618</v>
       </c>
-      <c r="AA41" s="2" t="n">
+      <c r="AC41" s="4" t="n">
         <v>0.2172879235051239</v>
       </c>
-      <c r="AB41" s="2" t="n">
+      <c r="AD41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AC41" s="2" t="n">
+      <c r="AE41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AD41" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE41" s="2" t="n">
+      <c r="AF41" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG41" s="3" t="n">
         <v>5678644</v>
       </c>
-      <c r="AF41" s="2" t="n">
+      <c r="AH41" s="3" t="n">
         <v>6692064</v>
       </c>
-      <c r="AG41" s="2" t="n">
+      <c r="AI41" s="3" t="n">
         <v>6692064.016</v>
       </c>
     </row>
@@ -5642,123 +6060,133 @@
           <t>South Africa</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
         <v>1214470</v>
       </c>
-      <c r="C42" s="2" t="n">
+      <c r="E42" s="3" t="n">
         <v>61089926</v>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="F42" s="4" t="n">
         <v>0.0106</v>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="G42" s="4" t="n">
         <v>0.272</v>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="H42" s="4" t="n">
         <v>0.653</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="I42" s="4" t="n">
         <v>0.075</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>30.7 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
+      <c r="K42" s="4" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>Black African 80.9%, Colored 8.8%, White 7.8%, Indian/Asian 2.6%  (2021 est.)</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>Christian 86%, ancestral, tribal, animist, or other traditional African religions 5.4%, Muslim 1.9%, other 1.5%, nothing in particular 5.2% (2015 est.)</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">isiZulu (official) 24.7%, isiXhosa (official) 15.6%, Afrikaans (official) 12.1%, Sepedi (official) 9.8%, Setswana (official) 8.9%, English (official) 8.4%, Sesotho (official) 8%, Xitsonga (official) 4%, siSwati (official) 2.6%, Tshivenda (official) 2.5%, isiNdebele (official) 1.6%, other (includes Khoi, Nama, and San languages) 1.9% </t>
         </is>
       </c>
-      <c r="M42" s="2" t="n">
+      <c r="O42" s="4" t="n">
         <v>0.912</v>
       </c>
-      <c r="N42" s="2" t="n">
+      <c r="P42" s="4" t="n">
         <v>0.877</v>
       </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">86.5% </t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr">
+      <c r="R42" s="2" t="inlineStr">
         <is>
           <t>9 provinces</t>
         </is>
       </c>
-      <c r="Q42" s="2" t="inlineStr">
+      <c r="S42" s="2" t="inlineStr">
         <is>
           <t>$400.261 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R42" s="2" t="n">
+      <c r="T42" s="4" t="n">
         <v>0.006</v>
       </c>
-      <c r="S42" s="2" t="inlineStr">
+      <c r="U42" s="2" t="inlineStr">
         <is>
           <t>$13,600 (2024 est.)</t>
         </is>
       </c>
-      <c r="T42" s="2" t="inlineStr">
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>33.2% (2024 est.)</t>
         </is>
       </c>
-      <c r="U42" s="2" t="inlineStr">
+      <c r="W42" s="2" t="inlineStr">
         <is>
           <t>55.5% (2014 est.)</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="X42" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 1.2%
 highest 10%: 51.3% (2011 est.)</t>
         </is>
       </c>
-      <c r="W42" s="2" t="n">
+      <c r="Y42" s="4" t="n">
         <v>0.044</v>
       </c>
-      <c r="X42" s="2" t="n">
+      <c r="Z42" s="3" t="n">
         <v>96972459</v>
       </c>
-      <c r="Y42" s="2" t="n">
+      <c r="AA42" s="4" t="n">
         <v>1.587372343518635</v>
       </c>
-      <c r="Z42" s="2" t="n">
+      <c r="AB42" s="3" t="n">
         <v>31107064</v>
       </c>
-      <c r="AA42" s="2" t="n">
+      <c r="AC42" s="4" t="n">
         <v>0.5092012061039327</v>
       </c>
-      <c r="AB42" s="2" t="n">
+      <c r="AD42" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="AC42" s="2" t="n">
+      <c r="AE42" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AD42" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE42" s="2" t="n">
+      <c r="AF42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG42" s="3" t="n">
         <v>42029869</v>
       </c>
-      <c r="AF42" s="2" t="n">
+      <c r="AH42" s="3" t="n">
         <v>16616460</v>
       </c>
-      <c r="AG42" s="2" t="n">
+      <c r="AI42" s="3" t="n">
         <v>33904908.93</v>
       </c>
     </row>
@@ -5768,121 +6196,131 @@
           <t>Botswana</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>RoSSA</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>EESA</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
         <v>566730</v>
       </c>
-      <c r="C43" s="2" t="n">
+      <c r="E43" s="3" t="n">
         <v>2521534</v>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="F43" s="4" t="n">
         <v>0.0132</v>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="G43" s="4" t="n">
         <v>0.287</v>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="H43" s="4" t="n">
         <v>0.652</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="I43" s="4" t="n">
         <v>0.061</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>25.8 years (2025 est.)</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
+      <c r="K43" s="4" t="n">
         <v>0.7290000000000001</v>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>Tswana (or Setswana) 79%, Kalanga 11%, Basarwa 3%, other, including Kgalagadi and people of European ancestry 7%</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>Christian 79.1%, Badimo 4.1%, other 1.4% (includes Baha'i, Hindu, Muslim, Rastafarian), none 15.2%, unspecified 0.3% (2011 est.)</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>Setswana 77.3%, Sekalanga 7.4%, Shekgalagadi 3.4%, English (official) 2.8%, Zezuru/Shona 2%, Sesarwa 1.7%, Sembukushu 1.6%, Ndebele 1%, other 2.8% (2011 est.)</t>
         </is>
       </c>
-      <c r="M43" s="2" t="n">
+      <c r="O43" s="4" t="n">
         <v>0.885</v>
       </c>
-      <c r="N43" s="2" t="n">
+      <c r="P43" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="O43" s="2" t="n">
+      <c r="Q43" s="4" t="n">
         <v>0.889</v>
       </c>
-      <c r="P43" s="2" t="inlineStr">
+      <c r="R43" s="2" t="inlineStr">
         <is>
           <t>10 districts and 6 town</t>
         </is>
       </c>
-      <c r="Q43" s="2" t="inlineStr">
+      <c r="S43" s="2" t="inlineStr">
         <is>
           <t>$19.401 billion (2024 est.)</t>
         </is>
       </c>
-      <c r="R43" s="2" t="n">
+      <c r="T43" s="4" t="n">
         <v>0.03</v>
       </c>
-      <c r="S43" s="2" t="inlineStr">
+      <c r="U43" s="2" t="inlineStr">
         <is>
           <t>$18,100 (2024 est.)</t>
         </is>
       </c>
-      <c r="T43" s="2" t="inlineStr">
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>23.2% (2024 est.)</t>
         </is>
       </c>
-      <c r="U43" s="2" t="inlineStr">
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>16.1% (2015 est.)</t>
         </is>
       </c>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: NA
 highest 10%: NA</t>
         </is>
       </c>
-      <c r="W43" s="2" t="n">
+      <c r="Y43" s="4" t="n">
         <v>0.028</v>
       </c>
-      <c r="X43" s="2" t="n">
+      <c r="Z43" s="3" t="n">
         <v>3746760</v>
       </c>
-      <c r="Y43" s="2" t="n">
+      <c r="AA43" s="4" t="n">
         <v>1.48590500861777</v>
       </c>
-      <c r="Z43" s="2" t="n">
+      <c r="AB43" s="3" t="n">
         <v>1057079</v>
       </c>
-      <c r="AA43" s="2" t="n">
+      <c r="AC43" s="4" t="n">
         <v>0.4192206014275437</v>
       </c>
-      <c r="AB43" s="2" t="n">
+      <c r="AD43" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AC43" s="2" t="n">
+      <c r="AE43" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AD43" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AE43" s="2" t="n">
+      <c r="AF43" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG43" s="3" t="n">
         <v>1838198</v>
       </c>
-      <c r="AF43" s="2" t="n">
+      <c r="AH43" s="3" t="n">
         <v>723680</v>
       </c>
-      <c r="AG43" s="2" t="n">
+      <c r="AI43" s="3" t="n">
         <v>405966.974</v>
       </c>
     </row>
@@ -5892,117 +6330,119 @@
           <t>India Ocean</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n">
-        <v/>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v/>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v/>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v/>
-      </c>
-      <c r="I44" s="2" t="n">
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I44" s="4" t="n">
         <v/>
       </c>
       <c r="J44" s="2" t="n">
         <v/>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K44" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>Hindu 79.8%, Muslim 14.2%, Christian 2.3%, Sikh 1.7%, other and unspecified 2%</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>Hindi 43.6%, Bengali 8%, Marathi 6.9%, Telugu 6.7%, Tamil 5.7%, Gujarati 4.6%, Urdu 4.2%, Kannada 3.6%, Odia 3.1%, Malayalam 2.9%, Punjabi 2.7%, Assamese 1.3%, Maithili 1.1%, other 5.6%</t>
         </is>
       </c>
-      <c r="M44" s="2" t="n">
+      <c r="O44" s="4" t="n">
         <v>0.744</v>
       </c>
-      <c r="N44" s="2" t="n">
+      <c r="P44" s="4" t="n">
         <v>0.824</v>
       </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="Q44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">65.8% </t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr">
+      <c r="R44" s="2" t="inlineStr">
         <is>
           <t>28 states</t>
         </is>
       </c>
-      <c r="Q44" s="2" t="n">
+      <c r="S44" s="2" t="n">
         <v>2835927000000</v>
       </c>
-      <c r="R44" s="2" t="inlineStr">
+      <c r="T44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">6.55% </t>
         </is>
       </c>
-      <c r="S44" s="2" t="n">
+      <c r="U44" s="2" t="n">
         <v>6700</v>
       </c>
-      <c r="T44" s="2" t="inlineStr">
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>8.5% (2016 est.)</t>
         </is>
       </c>
-      <c r="U44" s="2" t="inlineStr">
+      <c r="W44" s="2" t="inlineStr">
         <is>
           <t>21.9% (2011 est.)</t>
         </is>
       </c>
-      <c r="V44" s="2" t="inlineStr">
+      <c r="X44" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: 3.6%
 highest 10%: 29.8% (2011)</t>
         </is>
       </c>
-      <c r="W44" s="2" t="n">
+      <c r="Y44" s="4" t="n">
         <v>0.037</v>
       </c>
-      <c r="X44" s="2" t="n">
+      <c r="Z44" s="3" t="n">
         <v>1151480361</v>
       </c>
-      <c r="Y44" s="2" t="n">
-        <v/>
-      </c>
-      <c r="Z44" s="2" t="n">
+      <c r="AA44" s="4" t="n">
+        <v/>
+      </c>
+      <c r="AB44" s="3" t="n">
         <v>446759327</v>
       </c>
-      <c r="AA44" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AB44" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AC44" s="2" t="n">
+      <c r="AC44" s="4" t="n">
         <v/>
       </c>
       <c r="AD44" s="2" t="n">
         <v/>
       </c>
       <c r="AE44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AF44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AG44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF44" s="2" t="n">
+      <c r="AH44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AG44" s="2" t="n">
+      <c r="AI44" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6012,130 +6452,132 @@
           <t>Islands</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n">
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="3" t="n">
         <v>100250</v>
       </c>
-      <c r="C45" s="2" t="n">
+      <c r="E45" s="3" t="n">
         <v>354234</v>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="F45" s="4" t="n">
         <v>0.0097</v>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="G45" s="4" t="n">
         <v>0.2031</v>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">64.23% </t>
         </is>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="I45" s="4" t="n">
         <v>0.1547</v>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>37.1 years</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">93.9% </t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">homogeneous mixture of descendants of Norse and Celts 81%, population with foreign background 19% </t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>Evangelical Lutheran Church of Iceland (official) 67.2%, Roman Catholic 3.9%, Reykjavik Free Church 2.8%, Hafnarfjordur Free Church 2%, Asatru Association 1.2%, The Independent Congregation .9%, other religions 4% (includes Zuist and Pentecostal), none 6.7%, other or unspecified 11.3%</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>Icelandic, English, Nordic languages, German</t>
         </is>
       </c>
-      <c r="M45" s="2" t="n">
-        <v/>
-      </c>
-      <c r="N45" s="2" t="n">
-        <v/>
-      </c>
-      <c r="O45" s="2" t="n">
-        <v/>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
+      <c r="O45" s="4" t="n">
+        <v/>
+      </c>
+      <c r="P45" s="4" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="4" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
         <is>
           <t>69 municipalities</t>
         </is>
       </c>
-      <c r="Q45" s="2" t="inlineStr">
+      <c r="S45" s="2" t="inlineStr">
         <is>
           <t>$24.614 billion</t>
         </is>
       </c>
-      <c r="R45" s="2" t="n">
+      <c r="T45" s="4" t="n">
         <v>0.0457</v>
       </c>
-      <c r="S45" s="2" t="n">
+      <c r="U45" s="2" t="n">
         <v>55874</v>
       </c>
-      <c r="T45" s="2" t="inlineStr">
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>3.62% (2019 est.)</t>
         </is>
       </c>
-      <c r="U45" s="2" t="inlineStr">
+      <c r="W45" s="2" t="inlineStr">
         <is>
           <t>8.8% (2017 est.)</t>
         </is>
       </c>
-      <c r="V45" s="2" t="inlineStr">
+      <c r="X45" s="2" t="inlineStr">
         <is>
           <t>lowest 10%: NA
 highest 10%: NA</t>
         </is>
       </c>
-      <c r="W45" s="2" t="n">
+      <c r="Y45" s="4" t="n">
         <v>0.03</v>
       </c>
-      <c r="X45" s="2" t="n">
+      <c r="Z45" s="3" t="n">
         <v>413446</v>
       </c>
-      <c r="Y45" s="2" t="n">
-        <v/>
-      </c>
-      <c r="Z45" s="2" t="n">
+      <c r="AA45" s="4" t="n">
+        <v/>
+      </c>
+      <c r="AB45" s="3" t="n">
         <v>340117</v>
       </c>
-      <c r="AA45" s="2" t="n">
-        <v/>
-      </c>
-      <c r="AB45" s="2" t="n">
+      <c r="AC45" s="4" t="n">
+        <v/>
+      </c>
+      <c r="AD45" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="AC45" s="2" t="n">
+      <c r="AE45" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="AD45" s="2" t="inlineStr">
+      <c r="AF45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">354234 </t>
         </is>
       </c>
-      <c r="AE45" s="2" t="n">
+      <c r="AG45" s="3" t="n">
         <v>332979.96</v>
       </c>
-      <c r="AF45" s="2" t="n">
+      <c r="AH45" s="3" t="n">
         <v>71944.92540000001</v>
       </c>
-      <c r="AG45" s="2" t="n">
+      <c r="AI45" s="3" t="n">
         <v>31172.592</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG45"/>
+  <autoFilter ref="A1:AI45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>